--- a/SJA_ER_Model.xlsx
+++ b/SJA_ER_Model.xlsx
@@ -15,11 +15,11 @@
     <sheet name="Enums" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entities'!$A$1:$F$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Attributes'!$A$1:$G$312</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Relationships'!$A$1:$G$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CRUD Matrix'!$A$1:$F$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Enums'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entities'!$A$1:$F$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Attributes'!$A$1:$G$263</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Relationships'!$A$1:$G$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CRUD Matrix'!$A$1:$F$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Enums'!$A$1:$C$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -658,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -699,79 +699,91 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>36 (31 base tables + 3 planned + 2 derived views)</t>
+          <t>29 (28 base tables + 1 derived view)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Key convention</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Every entity has a surrogate id bigint PRIMARY KEY (GENERATED ALWAYS AS IDENTITY). Views have no id.</t>
+          <t>Excludes modules mapped to 'Coming soon' menus: Payments, Debts, Reports, Evaluations, Documents, Notifications, AI/Knowledge Base.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Foreign keys</t>
+          <t>Key convention</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>bigint columns ending _id referencing &lt;table&gt;(id).</t>
+          <t>Every entity has a surrogate id bigint PRIMARY KEY (GENERATED ALWAYS AS IDENTITY). Views have no id.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Enums</t>
+          <t>Foreign keys</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Modeled as PostgreSQL ENUM types — see the 'Enums' sheet.</t>
+          <t>bigint columns ending _id referencing &lt;table&gt;(id).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Derived note</t>
+          <t>Enums</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>trainer total/monthly hours = SUM(lesson duration) — computed, not stored.</t>
+          <t>Modeled as PostgreSQL ENUM types — see the 'Enums' sheet.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Sheets</t>
+          <t>Derived note</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Overview · Entities · Attributes · Relationships · CRUD Matrix · Enums</t>
+          <t>trainer total/monthly hours = SUM(lesson duration) — computed, not stored.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>Sheets</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Overview · Entities · Attributes · Relationships · CRUD Matrix · Enums</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>CRUD legend</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>C=Create R=Read U=Update D=Delete. 'NONE' = no CRUD point in the current system (planned or derived).</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>C=Create R=Read U=Update D=Delete. 'NONE' = no CRUD point in the current system (e.g. reference or derived).</t>
         </is>
       </c>
     </row>
@@ -786,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1645,7 +1657,7 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>payment</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -1665,7 +1677,7 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Tuition payment (Fina integration).</t>
+          <t>Recurring subscription the parent activates.</t>
         </is>
       </c>
     </row>
@@ -1675,242 +1687,32 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>module_progress</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>(composite — VIEW)</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Recurring subscription the parent activates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Documents</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>Uploaded document (contract, certificate, …).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>System notification / reminder to a user.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>Reporting output (templates, schedule, archive).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Evaluations of trainers/students/groups.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>knowledge_article</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>AI / Knowledge Base article.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>module_progress</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Derived</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>(composite — VIEW)</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
           <t>VIEW: student progress per module (computed).</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>debt</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Derived</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>(composite — VIEW)</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>VIEW: outstanding balance per student (computed from payments).</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F37"/>
+  <autoFilter ref="A1:F30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1921,7 +1723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G312"/>
+  <dimension ref="A1:G263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7793,7 +7595,7 @@
     <row r="250">
       <c r="A250" s="15" t="inlineStr">
         <is>
-          <t>payment</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="B250" s="16" t="inlineStr">
@@ -7852,7 +7654,7 @@
       <c r="A252" s="3" t="inlineStr"/>
       <c r="B252" s="17" t="inlineStr">
         <is>
-          <t>semester_id</t>
+          <t>parent_id</t>
         </is>
       </c>
       <c r="C252" s="17" t="inlineStr">
@@ -7867,7 +7669,7 @@
       </c>
       <c r="E252" s="19" t="inlineStr">
         <is>
-          <t>semester(id)</t>
+          <t>parent(id)</t>
         </is>
       </c>
       <c r="F252" s="23" t="inlineStr">
@@ -7881,12 +7683,12 @@
       <c r="A253" s="3" t="inlineStr"/>
       <c r="B253" s="17" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C253" s="21" t="inlineStr">
-        <is>
-          <t>numeric(10,2)</t>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="C253" s="17" t="inlineStr">
+        <is>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D253" s="22" t="inlineStr"/>
@@ -7902,116 +7704,108 @@
       <c r="A254" s="3" t="inlineStr"/>
       <c r="B254" s="17" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>activated_at</t>
         </is>
       </c>
       <c r="C254" s="21" t="inlineStr">
         <is>
-          <t>char(3)</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D254" s="22" t="inlineStr"/>
       <c r="E254" s="19" t="inlineStr"/>
-      <c r="F254" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G254" s="4" t="inlineStr">
-        <is>
-          <t>Default 'GEL'</t>
-        </is>
-      </c>
+      <c r="F254" s="23" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G254" s="4" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr"/>
       <c r="B255" s="17" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C255" s="21" t="inlineStr">
         <is>
-          <t>payment_status</t>
+          <t>numeric(10,2)</t>
         </is>
       </c>
       <c r="D255" s="22" t="inlineStr"/>
       <c r="E255" s="19" t="inlineStr"/>
-      <c r="F255" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G255" s="4" t="inlineStr">
-        <is>
-          <t>ENUM: paid/pending/unallocated/overdue</t>
-        </is>
-      </c>
+      <c r="F255" s="23" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G255" s="4" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr"/>
       <c r="B256" s="17" t="inlineStr">
         <is>
-          <t>due_date</t>
-        </is>
-      </c>
-      <c r="C256" s="17" t="inlineStr">
-        <is>
-          <t>date</t>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C256" s="21" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D256" s="22" t="inlineStr"/>
       <c r="E256" s="19" t="inlineStr"/>
-      <c r="F256" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
+      <c r="F256" s="20" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="G256" s="4" t="inlineStr"/>
     </row>
-    <row r="257">
-      <c r="A257" s="3" t="inlineStr"/>
-      <c r="B257" s="17" t="inlineStr">
-        <is>
-          <t>paid_at</t>
-        </is>
-      </c>
-      <c r="C257" s="21" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D257" s="22" t="inlineStr"/>
-      <c r="E257" s="19" t="inlineStr"/>
-      <c r="F257" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G257" s="4" t="inlineStr"/>
+    <row r="257" ht="4" customHeight="1">
+      <c r="A257" s="25" t="n"/>
+      <c r="B257" s="25" t="n"/>
+      <c r="C257" s="25" t="n"/>
+      <c r="D257" s="25" t="n"/>
+      <c r="E257" s="25" t="n"/>
+      <c r="F257" s="25" t="n"/>
+      <c r="G257" s="25" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="3" t="inlineStr"/>
+      <c r="A258" s="15" t="inlineStr">
+        <is>
+          <t>module_progress</t>
+        </is>
+      </c>
       <c r="B258" s="17" t="inlineStr">
         <is>
-          <t>external_ref</t>
-        </is>
-      </c>
-      <c r="C258" s="21" t="inlineStr">
-        <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="D258" s="22" t="inlineStr"/>
-      <c r="E258" s="19" t="inlineStr"/>
-      <c r="F258" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
+          <t>student_id</t>
+        </is>
+      </c>
+      <c r="C258" s="17" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D258" s="24" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E258" s="19" t="inlineStr">
+        <is>
+          <t>student(id)</t>
+        </is>
+      </c>
+      <c r="F258" s="20" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="G258" s="4" t="inlineStr">
         <is>
-          <t>Fina reference</t>
+          <t>Part of composite key</t>
         </is>
       </c>
     </row>
@@ -8019,1206 +7813,121 @@
       <c r="A259" s="3" t="inlineStr"/>
       <c r="B259" s="17" t="inlineStr">
         <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C259" s="21" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D259" s="22" t="inlineStr"/>
-      <c r="E259" s="19" t="inlineStr"/>
+          <t>module_id</t>
+        </is>
+      </c>
+      <c r="C259" s="17" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="D259" s="24" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E259" s="19" t="inlineStr">
+        <is>
+          <t>module(id)</t>
+        </is>
+      </c>
       <c r="F259" s="20" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G259" s="4" t="inlineStr"/>
-    </row>
-    <row r="260" ht="4" customHeight="1">
-      <c r="A260" s="25" t="n"/>
-      <c r="B260" s="25" t="n"/>
-      <c r="C260" s="25" t="n"/>
-      <c r="D260" s="25" t="n"/>
-      <c r="E260" s="25" t="n"/>
-      <c r="F260" s="25" t="n"/>
-      <c r="G260" s="25" t="n"/>
+      <c r="G259" s="4" t="inlineStr">
+        <is>
+          <t>Part of composite key</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr"/>
+      <c r="B260" s="17" t="inlineStr">
+        <is>
+          <t>completed_lectures</t>
+        </is>
+      </c>
+      <c r="C260" s="17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D260" s="22" t="inlineStr"/>
+      <c r="E260" s="19" t="inlineStr"/>
+      <c r="F260" s="20" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="G260" s="4" t="inlineStr">
+        <is>
+          <t>Computed</t>
+        </is>
+      </c>
     </row>
     <row r="261">
-      <c r="A261" s="15" t="inlineStr">
-        <is>
-          <t>subscription</t>
-        </is>
-      </c>
-      <c r="B261" s="16" t="inlineStr">
-        <is>
-          <t>id</t>
+      <c r="A261" s="3" t="inlineStr"/>
+      <c r="B261" s="17" t="inlineStr">
+        <is>
+          <t>total_lectures</t>
         </is>
       </c>
       <c r="C261" s="17" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D261" s="18" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D261" s="22" t="inlineStr"/>
       <c r="E261" s="19" t="inlineStr"/>
       <c r="F261" s="20" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G261" s="4" t="inlineStr"/>
+      <c r="G261" s="4" t="inlineStr">
+        <is>
+          <t>Computed</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr"/>
       <c r="B262" s="17" t="inlineStr">
         <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="C262" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D262" s="24" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E262" s="19" t="inlineStr">
-        <is>
-          <t>student(id)</t>
-        </is>
-      </c>
+          <t>progress_pct</t>
+        </is>
+      </c>
+      <c r="C262" s="21" t="inlineStr">
+        <is>
+          <t>numeric(5,2)</t>
+        </is>
+      </c>
+      <c r="D262" s="22" t="inlineStr"/>
+      <c r="E262" s="19" t="inlineStr"/>
       <c r="F262" s="20" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="G262" s="4" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="3" t="inlineStr"/>
-      <c r="B263" s="17" t="inlineStr">
-        <is>
-          <t>parent_id</t>
-        </is>
-      </c>
-      <c r="C263" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D263" s="24" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E263" s="19" t="inlineStr">
-        <is>
-          <t>parent(id)</t>
-        </is>
-      </c>
-      <c r="F263" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G263" s="4" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="3" t="inlineStr"/>
-      <c r="B264" s="17" t="inlineStr">
-        <is>
-          <t>is_active</t>
-        </is>
-      </c>
-      <c r="C264" s="17" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="D264" s="22" t="inlineStr"/>
-      <c r="E264" s="19" t="inlineStr"/>
-      <c r="F264" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G264" s="4" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="3" t="inlineStr"/>
-      <c r="B265" s="17" t="inlineStr">
-        <is>
-          <t>activated_at</t>
-        </is>
-      </c>
-      <c r="C265" s="21" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D265" s="22" t="inlineStr"/>
-      <c r="E265" s="19" t="inlineStr"/>
-      <c r="F265" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G265" s="4" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="3" t="inlineStr"/>
-      <c r="B266" s="17" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C266" s="21" t="inlineStr">
-        <is>
-          <t>numeric(10,2)</t>
-        </is>
-      </c>
-      <c r="D266" s="22" t="inlineStr"/>
-      <c r="E266" s="19" t="inlineStr"/>
-      <c r="F266" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G266" s="4" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="3" t="inlineStr"/>
-      <c r="B267" s="17" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C267" s="21" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D267" s="22" t="inlineStr"/>
-      <c r="E267" s="19" t="inlineStr"/>
-      <c r="F267" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G267" s="4" t="inlineStr"/>
-    </row>
-    <row r="268" ht="4" customHeight="1">
-      <c r="A268" s="25" t="n"/>
-      <c r="B268" s="25" t="n"/>
-      <c r="C268" s="25" t="n"/>
-      <c r="D268" s="25" t="n"/>
-      <c r="E268" s="25" t="n"/>
-      <c r="F268" s="25" t="n"/>
-      <c r="G268" s="25" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="15" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="B269" s="16" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C269" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D269" s="18" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E269" s="19" t="inlineStr"/>
-      <c r="F269" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G269" s="4" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr"/>
-      <c r="B270" s="17" t="inlineStr">
-        <is>
-          <t>owner_user_id</t>
-        </is>
-      </c>
-      <c r="C270" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D270" s="24" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E270" s="19" t="inlineStr">
-        <is>
-          <t>app_user(id)</t>
-        </is>
-      </c>
-      <c r="F270" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G270" s="4" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="3" t="inlineStr"/>
-      <c r="B271" s="17" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="C271" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D271" s="24" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E271" s="19" t="inlineStr">
-        <is>
-          <t>student(id)</t>
-        </is>
-      </c>
-      <c r="F271" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G271" s="4" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="3" t="inlineStr"/>
-      <c r="B272" s="17" t="inlineStr">
-        <is>
-          <t>doc_type</t>
-        </is>
-      </c>
-      <c r="C272" s="21" t="inlineStr">
-        <is>
-          <t>varchar(60)</t>
-        </is>
-      </c>
-      <c r="D272" s="22" t="inlineStr"/>
-      <c r="E272" s="19" t="inlineStr"/>
-      <c r="F272" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G272" s="4" t="inlineStr">
-        <is>
-          <t>contract/document/certificate/other</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="3" t="inlineStr"/>
-      <c r="B273" s="17" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C273" s="21" t="inlineStr">
-        <is>
-          <t>varchar(160)</t>
-        </is>
-      </c>
-      <c r="D273" s="22" t="inlineStr"/>
-      <c r="E273" s="19" t="inlineStr"/>
-      <c r="F273" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G273" s="4" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="3" t="inlineStr"/>
-      <c r="B274" s="17" t="inlineStr">
-        <is>
-          <t>file_url</t>
-        </is>
-      </c>
-      <c r="C274" s="21" t="inlineStr">
-        <is>
-          <t>varchar(500)</t>
-        </is>
-      </c>
-      <c r="D274" s="22" t="inlineStr"/>
-      <c r="E274" s="19" t="inlineStr"/>
-      <c r="F274" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G274" s="4" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="3" t="inlineStr"/>
-      <c r="B275" s="17" t="inlineStr">
-        <is>
-          <t>uploaded_by</t>
-        </is>
-      </c>
-      <c r="C275" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D275" s="24" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E275" s="19" t="inlineStr">
-        <is>
-          <t>app_user(id)</t>
-        </is>
-      </c>
-      <c r="F275" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G275" s="4" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="3" t="inlineStr"/>
-      <c r="B276" s="17" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C276" s="21" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D276" s="22" t="inlineStr"/>
-      <c r="E276" s="19" t="inlineStr"/>
-      <c r="F276" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G276" s="4" t="inlineStr"/>
-    </row>
-    <row r="277" ht="4" customHeight="1">
-      <c r="A277" s="25" t="n"/>
-      <c r="B277" s="25" t="n"/>
-      <c r="C277" s="25" t="n"/>
-      <c r="D277" s="25" t="n"/>
-      <c r="E277" s="25" t="n"/>
-      <c r="F277" s="25" t="n"/>
-      <c r="G277" s="25" t="n"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="15" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="B278" s="16" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C278" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D278" s="18" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E278" s="19" t="inlineStr"/>
-      <c r="F278" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G278" s="4" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="3" t="inlineStr"/>
-      <c r="B279" s="17" t="inlineStr">
-        <is>
-          <t>recipient_user_id</t>
-        </is>
-      </c>
-      <c r="C279" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D279" s="24" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E279" s="19" t="inlineStr">
-        <is>
-          <t>app_user(id)</t>
-        </is>
-      </c>
-      <c r="F279" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G279" s="4" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="3" t="inlineStr"/>
-      <c r="B280" s="17" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="C280" s="17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D280" s="22" t="inlineStr"/>
-      <c r="E280" s="19" t="inlineStr"/>
-      <c r="F280" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G280" s="4" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="3" t="inlineStr"/>
-      <c r="B281" s="17" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="C281" s="21" t="inlineStr">
-        <is>
-          <t>notification_channel</t>
-        </is>
-      </c>
-      <c r="D281" s="22" t="inlineStr"/>
-      <c r="E281" s="19" t="inlineStr"/>
-      <c r="F281" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G281" s="4" t="inlineStr">
-        <is>
-          <t>ENUM: sms/email/push/in_app</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="3" t="inlineStr"/>
-      <c r="B282" s="17" t="inlineStr">
-        <is>
-          <t>escalation_level</t>
-        </is>
-      </c>
-      <c r="C282" s="17" t="inlineStr">
-        <is>
-          <t>smallint</t>
-        </is>
-      </c>
-      <c r="D282" s="22" t="inlineStr"/>
-      <c r="E282" s="19" t="inlineStr"/>
-      <c r="F282" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G282" s="4" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="3" t="inlineStr"/>
-      <c r="B283" s="17" t="inlineStr">
-        <is>
-          <t>sent_at</t>
-        </is>
-      </c>
-      <c r="C283" s="21" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D283" s="22" t="inlineStr"/>
-      <c r="E283" s="19" t="inlineStr"/>
-      <c r="F283" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G283" s="4" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="3" t="inlineStr"/>
-      <c r="B284" s="17" t="inlineStr">
-        <is>
-          <t>is_read</t>
-        </is>
-      </c>
-      <c r="C284" s="17" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="D284" s="22" t="inlineStr"/>
-      <c r="E284" s="19" t="inlineStr"/>
-      <c r="F284" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G284" s="4" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="3" t="inlineStr"/>
-      <c r="B285" s="17" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C285" s="21" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D285" s="22" t="inlineStr"/>
-      <c r="E285" s="19" t="inlineStr"/>
-      <c r="F285" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G285" s="4" t="inlineStr"/>
-    </row>
-    <row r="286" ht="4" customHeight="1">
-      <c r="A286" s="25" t="n"/>
-      <c r="B286" s="25" t="n"/>
-      <c r="C286" s="25" t="n"/>
-      <c r="D286" s="25" t="n"/>
-      <c r="E286" s="25" t="n"/>
-      <c r="F286" s="25" t="n"/>
-      <c r="G286" s="25" t="n"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="15" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="B287" s="16" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C287" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D287" s="18" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E287" s="19" t="inlineStr"/>
-      <c r="F287" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G287" s="4" t="inlineStr"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="3" t="inlineStr"/>
-      <c r="B288" s="17" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C288" s="21" t="inlineStr">
-        <is>
-          <t>varchar(160)</t>
-        </is>
-      </c>
-      <c r="D288" s="22" t="inlineStr"/>
-      <c r="E288" s="19" t="inlineStr"/>
-      <c r="F288" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G288" s="4" t="inlineStr"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="3" t="inlineStr"/>
-      <c r="B289" s="17" t="inlineStr">
-        <is>
-          <t>template_ref</t>
-        </is>
-      </c>
-      <c r="C289" s="21" t="inlineStr">
-        <is>
-          <t>varchar(120)</t>
-        </is>
-      </c>
-      <c r="D289" s="22" t="inlineStr"/>
-      <c r="E289" s="19" t="inlineStr"/>
-      <c r="F289" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G289" s="4" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="3" t="inlineStr"/>
-      <c r="B290" s="17" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C290" s="21" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D290" s="22" t="inlineStr"/>
-      <c r="E290" s="19" t="inlineStr"/>
-      <c r="F290" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G290" s="4" t="inlineStr"/>
-    </row>
-    <row r="291" ht="4" customHeight="1">
-      <c r="A291" s="25" t="n"/>
-      <c r="B291" s="25" t="n"/>
-      <c r="C291" s="25" t="n"/>
-      <c r="D291" s="25" t="n"/>
-      <c r="E291" s="25" t="n"/>
-      <c r="F291" s="25" t="n"/>
-      <c r="G291" s="25" t="n"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="15" t="inlineStr">
-        <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="B292" s="16" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C292" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D292" s="18" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E292" s="19" t="inlineStr"/>
-      <c r="F292" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G292" s="4" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="3" t="inlineStr"/>
-      <c r="B293" s="17" t="inlineStr">
-        <is>
-          <t>subject_type</t>
-        </is>
-      </c>
-      <c r="C293" s="21" t="inlineStr">
-        <is>
-          <t>varchar(40)</t>
-        </is>
-      </c>
-      <c r="D293" s="22" t="inlineStr"/>
-      <c r="E293" s="19" t="inlineStr"/>
-      <c r="F293" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G293" s="4" t="inlineStr">
-        <is>
-          <t>student/trainer/group</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="3" t="inlineStr"/>
-      <c r="B294" s="17" t="inlineStr">
-        <is>
-          <t>subject_id</t>
-        </is>
-      </c>
-      <c r="C294" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D294" s="22" t="inlineStr"/>
-      <c r="E294" s="19" t="inlineStr"/>
-      <c r="F294" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G294" s="4" t="inlineStr">
-        <is>
-          <t>Polymorphic ref</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="3" t="inlineStr"/>
-      <c r="B295" s="17" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="C295" s="21" t="inlineStr">
-        <is>
-          <t>numeric(5,2)</t>
-        </is>
-      </c>
-      <c r="D295" s="22" t="inlineStr"/>
-      <c r="E295" s="19" t="inlineStr"/>
-      <c r="F295" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G295" s="4" t="inlineStr"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="3" t="inlineStr"/>
-      <c r="B296" s="17" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C296" s="21" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D296" s="22" t="inlineStr"/>
-      <c r="E296" s="19" t="inlineStr"/>
-      <c r="F296" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G296" s="4" t="inlineStr"/>
-    </row>
-    <row r="297" ht="4" customHeight="1">
-      <c r="A297" s="25" t="n"/>
-      <c r="B297" s="25" t="n"/>
-      <c r="C297" s="25" t="n"/>
-      <c r="D297" s="25" t="n"/>
-      <c r="E297" s="25" t="n"/>
-      <c r="F297" s="25" t="n"/>
-      <c r="G297" s="25" t="n"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="15" t="inlineStr">
-        <is>
-          <t>knowledge_article</t>
-        </is>
-      </c>
-      <c r="B298" s="16" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C298" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D298" s="18" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E298" s="19" t="inlineStr"/>
-      <c r="F298" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G298" s="4" t="inlineStr"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="3" t="inlineStr"/>
-      <c r="B299" s="17" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C299" s="21" t="inlineStr">
-        <is>
-          <t>varchar(160)</t>
-        </is>
-      </c>
-      <c r="D299" s="22" t="inlineStr"/>
-      <c r="E299" s="19" t="inlineStr"/>
-      <c r="F299" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G299" s="4" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="3" t="inlineStr"/>
-      <c r="B300" s="17" t="inlineStr">
-        <is>
-          <t>body</t>
-        </is>
-      </c>
-      <c r="C300" s="17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D300" s="22" t="inlineStr"/>
-      <c r="E300" s="19" t="inlineStr"/>
-      <c r="F300" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G300" s="4" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="3" t="inlineStr"/>
-      <c r="B301" s="17" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C301" s="21" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="D301" s="22" t="inlineStr"/>
-      <c r="E301" s="19" t="inlineStr"/>
-      <c r="F301" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G301" s="4" t="inlineStr"/>
-    </row>
-    <row r="302" ht="4" customHeight="1">
-      <c r="A302" s="25" t="n"/>
-      <c r="B302" s="25" t="n"/>
-      <c r="C302" s="25" t="n"/>
-      <c r="D302" s="25" t="n"/>
-      <c r="E302" s="25" t="n"/>
-      <c r="F302" s="25" t="n"/>
-      <c r="G302" s="25" t="n"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="15" t="inlineStr">
-        <is>
-          <t>module_progress</t>
-        </is>
-      </c>
-      <c r="B303" s="17" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="C303" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D303" s="24" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E303" s="19" t="inlineStr">
-        <is>
-          <t>student(id)</t>
-        </is>
-      </c>
-      <c r="F303" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G303" s="4" t="inlineStr">
-        <is>
-          <t>Part of composite key</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="3" t="inlineStr"/>
-      <c r="B304" s="17" t="inlineStr">
-        <is>
-          <t>module_id</t>
-        </is>
-      </c>
-      <c r="C304" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D304" s="24" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E304" s="19" t="inlineStr">
-        <is>
-          <t>module(id)</t>
-        </is>
-      </c>
-      <c r="F304" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G304" s="4" t="inlineStr">
-        <is>
-          <t>Part of composite key</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="3" t="inlineStr"/>
-      <c r="B305" s="17" t="inlineStr">
-        <is>
-          <t>completed_lectures</t>
-        </is>
-      </c>
-      <c r="C305" s="17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D305" s="22" t="inlineStr"/>
-      <c r="E305" s="19" t="inlineStr"/>
-      <c r="F305" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G305" s="4" t="inlineStr">
+      <c r="G262" s="4" t="inlineStr">
         <is>
           <t>Computed</t>
         </is>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" s="3" t="inlineStr"/>
-      <c r="B306" s="17" t="inlineStr">
-        <is>
-          <t>total_lectures</t>
-        </is>
-      </c>
-      <c r="C306" s="17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D306" s="22" t="inlineStr"/>
-      <c r="E306" s="19" t="inlineStr"/>
-      <c r="F306" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G306" s="4" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="3" t="inlineStr"/>
-      <c r="B307" s="17" t="inlineStr">
-        <is>
-          <t>progress_pct</t>
-        </is>
-      </c>
-      <c r="C307" s="21" t="inlineStr">
-        <is>
-          <t>numeric(5,2)</t>
-        </is>
-      </c>
-      <c r="D307" s="22" t="inlineStr"/>
-      <c r="E307" s="19" t="inlineStr"/>
-      <c r="F307" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G307" s="4" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="308" ht="4" customHeight="1">
-      <c r="A308" s="25" t="n"/>
-      <c r="B308" s="25" t="n"/>
-      <c r="C308" s="25" t="n"/>
-      <c r="D308" s="25" t="n"/>
-      <c r="E308" s="25" t="n"/>
-      <c r="F308" s="25" t="n"/>
-      <c r="G308" s="25" t="n"/>
-    </row>
-    <row r="309">
-      <c r="A309" s="15" t="inlineStr">
-        <is>
-          <t>debt</t>
-        </is>
-      </c>
-      <c r="B309" s="17" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="C309" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D309" s="24" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E309" s="19" t="inlineStr">
-        <is>
-          <t>student(id)</t>
-        </is>
-      </c>
-      <c r="F309" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G309" s="4" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="3" t="inlineStr"/>
-      <c r="B310" s="17" t="inlineStr">
-        <is>
-          <t>outstanding_amount</t>
-        </is>
-      </c>
-      <c r="C310" s="21" t="inlineStr">
-        <is>
-          <t>numeric(10,2)</t>
-        </is>
-      </c>
-      <c r="D310" s="22" t="inlineStr"/>
-      <c r="E310" s="19" t="inlineStr"/>
-      <c r="F310" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G310" s="4" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="3" t="inlineStr"/>
-      <c r="B311" s="17" t="inlineStr">
-        <is>
-          <t>overdue_days</t>
-        </is>
-      </c>
-      <c r="C311" s="17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D311" s="22" t="inlineStr"/>
-      <c r="E311" s="19" t="inlineStr"/>
-      <c r="F311" s="23" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G311" s="4" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="312" ht="4" customHeight="1">
-      <c r="A312" s="25" t="n"/>
-      <c r="B312" s="25" t="n"/>
-      <c r="C312" s="25" t="n"/>
-      <c r="D312" s="25" t="n"/>
-      <c r="E312" s="25" t="n"/>
-      <c r="F312" s="25" t="n"/>
-      <c r="G312" s="25" t="n"/>
+    <row r="263" ht="4" customHeight="1">
+      <c r="A263" s="25" t="n"/>
+      <c r="B263" s="25" t="n"/>
+      <c r="C263" s="25" t="n"/>
+      <c r="D263" s="25" t="n"/>
+      <c r="E263" s="25" t="n"/>
+      <c r="F263" s="25" t="n"/>
+      <c r="G263" s="25" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G312"/>
+  <autoFilter ref="A1:G263"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9229,7 +7938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11209,7 +9918,7 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>payment</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
@@ -11234,7 +9943,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>payment → student</t>
+          <t>subscription → student</t>
         </is>
       </c>
     </row>
@@ -11244,17 +9953,17 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>payment</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>semester_id</t>
+          <t>parent_id</t>
         </is>
       </c>
       <c r="D58" s="27" t="inlineStr">
         <is>
-          <t>semester(id)</t>
+          <t>parent(id)</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -11269,7 +9978,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>payment → semester</t>
+          <t>subscription → parent</t>
         </is>
       </c>
     </row>
@@ -11279,7 +9988,7 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>module_progress</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
@@ -11304,7 +10013,7 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>subscription → student</t>
+          <t>Part of composite key</t>
         </is>
       </c>
     </row>
@@ -11314,17 +10023,17 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>module_progress</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>parent_id</t>
+          <t>module_id</t>
         </is>
       </c>
       <c r="D60" s="27" t="inlineStr">
         <is>
-          <t>parent(id)</t>
+          <t>module(id)</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -11334,335 +10043,90 @@
       </c>
       <c r="F60" s="28" t="inlineStr">
         <is>
-          <t>SET NULL</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>subscription → parent</t>
+          <t>Part of composite key</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>owner_user_id</t>
-        </is>
-      </c>
-      <c r="D61" s="29" t="inlineStr">
-        <is>
-          <t>app_user(id)</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>N:1</t>
-        </is>
-      </c>
-      <c r="F61" s="30" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="G61" s="12" t="inlineStr">
-        <is>
-          <t>document → app_user</t>
+      <c r="B61" s="31" t="inlineStr">
+        <is>
+          <t>— Many-to-many resolutions —</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="D62" s="27" t="inlineStr">
-        <is>
-          <t>student(id)</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>N:1</t>
-        </is>
-      </c>
-      <c r="F62" s="28" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="G62" s="8" t="inlineStr">
-        <is>
-          <t>document → student</t>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>student_parent</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>student ↔ parent</t>
+        </is>
+      </c>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>M:N</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>via student_parent</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="inlineStr">
-        <is>
-          <t>uploaded_by</t>
-        </is>
-      </c>
-      <c r="D63" s="29" t="inlineStr">
-        <is>
-          <t>app_user(id)</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>N:1</t>
-        </is>
-      </c>
-      <c r="F63" s="30" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="G63" s="12" t="inlineStr">
-        <is>
-          <t>document → app_user</t>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>group_membership</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>student ↔ study_group</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="inlineStr">
+        <is>
+          <t>M:N</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>via group_membership</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>recipient_user_id</t>
-        </is>
-      </c>
-      <c r="D64" s="27" t="inlineStr">
-        <is>
-          <t>app_user(id)</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>N:1</t>
-        </is>
-      </c>
-      <c r="F64" s="28" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>notification → app_user</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>module_progress</t>
-        </is>
-      </c>
-      <c r="C65" s="13" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="D65" s="29" t="inlineStr">
-        <is>
-          <t>student(id)</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>N:1</t>
-        </is>
-      </c>
-      <c r="F65" s="30" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="G65" s="12" t="inlineStr">
-        <is>
-          <t>Part of composite key</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>module_progress</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>module_id</t>
-        </is>
-      </c>
-      <c r="D66" s="27" t="inlineStr">
-        <is>
-          <t>module(id)</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>N:1</t>
-        </is>
-      </c>
-      <c r="F66" s="28" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
-        <is>
-          <t>Part of composite key</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>debt</t>
-        </is>
-      </c>
-      <c r="C67" s="13" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="D67" s="29" t="inlineStr">
-        <is>
-          <t>student(id)</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>N:1</t>
-        </is>
-      </c>
-      <c r="F67" s="30" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="G67" s="12" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="31" t="inlineStr">
-        <is>
-          <t>— Many-to-many resolutions —</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>student_parent</t>
-        </is>
-      </c>
-      <c r="D69" s="19" t="inlineStr">
-        <is>
-          <t>student ↔ parent</t>
-        </is>
-      </c>
-      <c r="E69" s="22" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>project_participation</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>student ↔ project</t>
+        </is>
+      </c>
+      <c r="E64" s="22" t="inlineStr">
         <is>
           <t>M:N</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>via student_parent</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>group_membership</t>
-        </is>
-      </c>
-      <c r="D70" s="19" t="inlineStr">
-        <is>
-          <t>student ↔ study_group</t>
-        </is>
-      </c>
-      <c r="E70" s="22" t="inlineStr">
-        <is>
-          <t>M:N</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>via group_membership</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>project_participation</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr">
-        <is>
-          <t>student ↔ project</t>
-        </is>
-      </c>
-      <c r="E71" s="22" t="inlineStr">
-        <is>
-          <t>M:N</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>via project_participation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G67"/>
+  <autoFilter ref="A1:G60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11673,7 +10137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12140,17 +10604,17 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Module Templates</t>
+          <t>Module Templates › category (mAddTemplate)</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Module Templates grid + template detail</t>
+          <t>Module Templates grid → category list → template detail</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Template detail</t>
+          <t>Template detail / Edit Lecture</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -12204,7 +10668,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Learning Modules (mAddModule)</t>
+          <t>Learning Modules › instantiate template (mAddModule)</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -12214,7 +10678,7 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Module detail</t>
+          <t>Module detail / Edit Lecture</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -12583,22 +11047,22 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>payment</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Fina integration (auto) + manual entry</t>
+          <t>Parent portal (activate)</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Payments / Finance</t>
+          <t>Parent / Admin finance</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Allocate unallocated</t>
+          <t>Activate / cancel</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -12608,280 +11072,56 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>CRU (create mostly external)</t>
+          <t>CRU</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>subscription</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Parent portal (activate)</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Parent / Admin finance</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Activate / cancel</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>module_progress</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>CRU</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>Documents (mAddDocument)</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Documents list</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>Student profile progress; dashboards</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>Delete</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>CRD</t>
+      <c r="E30" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>NONE — derived VIEW (no id; read-only)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>System-generated (auto rules)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Notifications screen</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Mark read / settings</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>RU (create is system, not manual)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>report</t>
-        </is>
-      </c>
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C33" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="34" t="inlineStr">
-        <is>
-          <t>NONE — 'Coming soon', no CRUD point yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="32" t="inlineStr">
-        <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C34" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="34" t="inlineStr">
-        <is>
-          <t>NONE — 'Coming soon', no CRUD point yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t>knowledge_article</t>
-        </is>
-      </c>
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C35" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="34" t="inlineStr">
-        <is>
-          <t>NONE — 'Coming soon', no CRUD point yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="32" t="inlineStr">
-        <is>
-          <t>module_progress</t>
-        </is>
-      </c>
-      <c r="B36" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C36" s="33" t="inlineStr">
-        <is>
-          <t>Student profile progress; dashboards</t>
-        </is>
-      </c>
-      <c r="D36" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="34" t="inlineStr">
-        <is>
-          <t>NONE — derived VIEW (no id; read-only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t>debt</t>
-        </is>
-      </c>
-      <c r="B37" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C37" s="33" t="inlineStr">
-        <is>
-          <t>Finance › Debts</t>
-        </is>
-      </c>
-      <c r="D37" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="34" t="inlineStr">
-        <is>
-          <t>NONE — derived VIEW (read-only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>Entities with NO CRUD point:</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>program, report, evaluation, knowledge_article, module_progress, debt</t>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>program, module_progress</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F37"/>
+  <autoFilter ref="A1:F30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12892,7 +11132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -13073,90 +11313,56 @@
     <row r="11">
       <c r="A11" s="37" t="inlineStr">
         <is>
-          <t>payment_status</t>
+          <t>intake_season</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>paid, pending, unallocated, overdue</t>
+          <t>spring, autumn</t>
         </is>
       </c>
       <c r="C11" s="38" t="inlineStr">
         <is>
-          <t>payment.status</t>
+          <t>intake.season</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>intake_season</t>
+          <t>relationship_type</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>spring, autumn</t>
+          <t>mother, father, guardian, other</t>
         </is>
       </c>
       <c r="C12" s="36" t="inlineStr">
         <is>
-          <t>intake.season</t>
+          <t>student_parent.relationship</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="37" t="inlineStr">
         <is>
-          <t>relationship_type</t>
+          <t>project_result</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>mother, father, guardian, other</t>
+          <t>participated, won, completed</t>
         </is>
       </c>
       <c r="C13" s="38" t="inlineStr">
         <is>
-          <t>student_parent.relationship</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>project_result</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>participated, won, completed</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
           <t>project_participation.result</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="37" t="inlineStr">
-        <is>
-          <t>notification_channel</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>sms, email, push, in_app</t>
-        </is>
-      </c>
-      <c r="C15" s="38" t="inlineStr">
-        <is>
-          <t>notification.channel</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C15"/>
+  <autoFilter ref="A1:C13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/SJA_ER_Model.xlsx
+++ b/SJA_ER_Model.xlsx
@@ -15,10 +15,10 @@
     <sheet name="Enums" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entities'!$A$1:$F$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Attributes'!$A$1:$G$259</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Relationships'!$A$1:$G$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CRUD Matrix'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entities'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Attributes'!$A$1:$G$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Relationships'!$A$1:$G$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CRUD Matrix'!$A$1:$F$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Enums'!$A$1:$C$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,17 +100,11 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00B23A4B"/>
-      <sz val="9.5"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="007A2E8A"/>
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -130,11 +124,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F6F8FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBE3E7"/>
       </patternFill>
     </fill>
     <fill>
@@ -179,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -220,10 +209,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -232,7 +218,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -250,7 +236,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -272,22 +258,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -658,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -699,7 +676,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>28 (27 base tables + 1 derived view)</t>
+          <t>27 base tables (no views)</t>
         </is>
       </c>
     </row>
@@ -730,70 +707,82 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Key convention</t>
+          <t>Module progress</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Every entity has a surrogate id bigint PRIMARY KEY (GENERATED ALWAYS AS IDENTITY). Views have no id.</t>
+          <t>The progress bar is the module's overall progress = conducted lectures / total lectures — an aggregate over module_lecture.is_conducted, not a stored per-student value.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Foreign keys</t>
+          <t>Key convention</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>bigint columns ending _id referencing &lt;table&gt;(id).</t>
+          <t>Every entity has a surrogate id bigint PRIMARY KEY (GENERATED ALWAYS AS IDENTITY). Views have no id.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Enums</t>
+          <t>Foreign keys</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Modeled as PostgreSQL ENUM types — see the 'Enums' sheet.</t>
+          <t>bigint columns ending _id referencing &lt;table&gt;(id).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Derived note</t>
+          <t>Enums</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>trainer total/monthly hours = SUM(lesson duration) — computed, not stored.</t>
+          <t>Modeled as PostgreSQL ENUM types — see the 'Enums' sheet.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Sheets</t>
+          <t>Derived note</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Overview · Entities · Attributes · Relationships · CRUD Matrix · Enums</t>
+          <t>trainer total/monthly hours = SUM(lesson duration) — computed, not stored.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>Sheets</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Overview · Entities · Attributes · Relationships · CRUD Matrix · Enums</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>CRUD legend</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>C=Create R=Read U=Update D=Delete. 'NONE' = no CRUD point in the current system (e.g. reference or derived).</t>
         </is>
@@ -810,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1663,38 +1652,8 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>module_progress</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Derived</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>(composite — VIEW)</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>VIEW: student progress per module (computed).</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F29"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1705,7 +1664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G259"/>
+  <dimension ref="A1:G253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1755,28 +1714,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>branch</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr"/>
-      <c r="F2" s="20" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr"/>
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -1789,19 +1748,19 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>varchar(120)</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr"/>
-      <c r="E3" s="19" t="inlineStr"/>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr"/>
+      <c r="E3" s="18" t="inlineStr"/>
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -1814,19 +1773,19 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>address</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr"/>
-      <c r="E4" s="19" t="inlineStr"/>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -1839,27 +1798,27 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>manager_id</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>staff_member(id)</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -1872,19 +1831,19 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>payment_due_day</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="19" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -1897,19 +1856,19 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr"/>
-      <c r="E7" s="19" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -1922,19 +1881,19 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr"/>
-      <c r="E8" s="19" t="inlineStr"/>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -1946,37 +1905,37 @@
       </c>
     </row>
     <row r="9" ht="4" customHeight="1">
-      <c r="A9" s="25" t="n"/>
-      <c r="B9" s="25" t="n"/>
-      <c r="C9" s="25" t="n"/>
-      <c r="D9" s="25" t="n"/>
-      <c r="E9" s="25" t="n"/>
-      <c r="F9" s="25" t="n"/>
-      <c r="G9" s="25" t="n"/>
+      <c r="A9" s="24" t="n"/>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>app_user</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -1985,23 +1944,23 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>personal_id</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>varchar(11)</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>UQ</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr"/>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2014,19 +1973,19 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>varchar(160)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr"/>
-      <c r="E12" s="19" t="inlineStr"/>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr"/>
+      <c r="E12" s="18" t="inlineStr"/>
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -2035,19 +1994,19 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>password_hash</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>varchar(255)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr"/>
-      <c r="E13" s="19" t="inlineStr"/>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr"/>
+      <c r="E13" s="18" t="inlineStr"/>
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -2060,19 +2019,19 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>user_role</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr"/>
-      <c r="E14" s="19" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr"/>
+      <c r="E14" s="18" t="inlineStr"/>
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2085,19 +2044,19 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr"/>
-      <c r="E15" s="19" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr"/>
+      <c r="E15" s="18" t="inlineStr"/>
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2106,19 +2065,19 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>last_login_at</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr"/>
-      <c r="E16" s="19" t="inlineStr"/>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr"/>
+      <c r="E16" s="18" t="inlineStr"/>
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -2127,19 +2086,19 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr"/>
-      <c r="E17" s="19" t="inlineStr"/>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr"/>
+      <c r="E17" s="18" t="inlineStr"/>
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2147,37 +2106,37 @@
       <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="4" customHeight="1">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="n"/>
-      <c r="G18" s="25" t="n"/>
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>age_category</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr"/>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr"/>
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2186,23 +2145,23 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>varchar(40)</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>UQ</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr"/>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr"/>
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2215,19 +2174,19 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr"/>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>entry_age_min</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr"/>
-      <c r="E21" s="19" t="inlineStr"/>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr"/>
+      <c r="E21" s="18" t="inlineStr"/>
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2236,19 +2195,19 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>entry_age_max</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr"/>
-      <c r="E22" s="19" t="inlineStr"/>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr"/>
+      <c r="E22" s="18" t="inlineStr"/>
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2257,19 +2216,19 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr"/>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>total_years</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr"/>
-      <c r="E23" s="19" t="inlineStr"/>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr"/>
+      <c r="E23" s="18" t="inlineStr"/>
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2282,19 +2241,19 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>total_semesters</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr"/>
-      <c r="E24" s="19" t="inlineStr"/>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr"/>
+      <c r="E24" s="18" t="inlineStr"/>
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2306,37 +2265,37 @@
       </c>
     </row>
     <row r="25" ht="4" customHeight="1">
-      <c r="A25" s="25" t="n"/>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="25" t="n"/>
-      <c r="G25" s="25" t="n"/>
+      <c r="A25" s="24" t="n"/>
+      <c r="B25" s="24" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="24" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>intake</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr"/>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr"/>
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2345,23 +2304,23 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr"/>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>varchar(40)</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="25" t="inlineStr">
         <is>
           <t>UQ</t>
         </is>
       </c>
-      <c r="E27" s="19" t="inlineStr"/>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr"/>
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2374,19 +2333,19 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr"/>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>intake_season</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr"/>
-      <c r="E28" s="19" t="inlineStr"/>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr"/>
+      <c r="E28" s="18" t="inlineStr"/>
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2399,19 +2358,19 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr"/>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr"/>
-      <c r="E29" s="19" t="inlineStr"/>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr"/>
+      <c r="E29" s="18" t="inlineStr"/>
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2420,19 +2379,19 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr"/>
-      <c r="E30" s="19" t="inlineStr"/>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr"/>
+      <c r="E30" s="18" t="inlineStr"/>
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2440,37 +2399,37 @@
       <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31" ht="4" customHeight="1">
-      <c r="A31" s="25" t="n"/>
-      <c r="B31" s="25" t="n"/>
-      <c r="C31" s="25" t="n"/>
-      <c r="D31" s="25" t="n"/>
-      <c r="E31" s="25" t="n"/>
-      <c r="F31" s="25" t="n"/>
-      <c r="G31" s="25" t="n"/>
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>semester</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E32" s="19" t="inlineStr"/>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr"/>
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2479,27 +2438,27 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr"/>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>branch_id</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E33" s="19" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2508,19 +2467,19 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr"/>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>varchar(60)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr"/>
-      <c r="E34" s="19" t="inlineStr"/>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr"/>
+      <c r="E34" s="18" t="inlineStr"/>
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2533,19 +2492,19 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr"/>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>starts_on</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr"/>
-      <c r="E35" s="19" t="inlineStr"/>
-      <c r="F35" s="20" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr"/>
+      <c r="E35" s="18" t="inlineStr"/>
+      <c r="F35" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2554,19 +2513,19 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr"/>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>ends_on</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr"/>
-      <c r="E36" s="19" t="inlineStr"/>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr"/>
+      <c r="E36" s="18" t="inlineStr"/>
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2575,19 +2534,19 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr"/>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>payment_due_day</t>
         </is>
       </c>
-      <c r="C37" s="17" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr"/>
-      <c r="E37" s="19" t="inlineStr"/>
-      <c r="F37" s="20" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr"/>
+      <c r="E37" s="18" t="inlineStr"/>
+      <c r="F37" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2596,19 +2555,19 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr"/>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr"/>
-      <c r="E38" s="19" t="inlineStr"/>
-      <c r="F38" s="20" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr"/>
+      <c r="E38" s="18" t="inlineStr"/>
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2616,37 +2575,37 @@
       <c r="G38" s="4" t="inlineStr"/>
     </row>
     <row r="39" ht="4" customHeight="1">
-      <c r="A39" s="25" t="n"/>
-      <c r="B39" s="25" t="n"/>
-      <c r="C39" s="25" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="25" t="n"/>
-      <c r="G39" s="25" t="n"/>
+      <c r="A39" s="24" t="n"/>
+      <c r="B39" s="24" t="n"/>
+      <c r="C39" s="24" t="n"/>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="24" t="n"/>
+      <c r="G39" s="24" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>student</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D40" s="18" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E40" s="19" t="inlineStr"/>
-      <c r="F40" s="20" t="inlineStr">
+      <c r="E40" s="18" t="inlineStr"/>
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2655,27 +2614,27 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr"/>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="C41" s="17" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D41" s="24" t="inlineStr">
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>app_user(id)</t>
         </is>
       </c>
-      <c r="F41" s="23" t="inlineStr">
+      <c r="F41" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -2688,23 +2647,23 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr"/>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>personal_id</t>
         </is>
       </c>
-      <c r="C42" s="21" t="inlineStr">
+      <c r="C42" s="20" t="inlineStr">
         <is>
           <t>varchar(11)</t>
         </is>
       </c>
-      <c r="D42" s="26" t="inlineStr">
+      <c r="D42" s="25" t="inlineStr">
         <is>
           <t>UQ</t>
         </is>
       </c>
-      <c r="E42" s="19" t="inlineStr"/>
-      <c r="F42" s="20" t="inlineStr">
+      <c r="E42" s="18" t="inlineStr"/>
+      <c r="F42" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2717,19 +2676,19 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr"/>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="C43" s="21" t="inlineStr">
+      <c r="C43" s="20" t="inlineStr">
         <is>
           <t>varchar(120)</t>
         </is>
       </c>
-      <c r="D43" s="22" t="inlineStr"/>
-      <c r="E43" s="19" t="inlineStr"/>
-      <c r="F43" s="20" t="inlineStr">
+      <c r="D43" s="21" t="inlineStr"/>
+      <c r="E43" s="18" t="inlineStr"/>
+      <c r="F43" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2738,19 +2697,19 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr"/>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>date_of_birth</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D44" s="22" t="inlineStr"/>
-      <c r="E44" s="19" t="inlineStr"/>
-      <c r="F44" s="20" t="inlineStr">
+      <c r="D44" s="21" t="inlineStr"/>
+      <c r="E44" s="18" t="inlineStr"/>
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2759,19 +2718,19 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr"/>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>citizenship</t>
         </is>
       </c>
-      <c r="C45" s="21" t="inlineStr">
+      <c r="C45" s="20" t="inlineStr">
         <is>
           <t>varchar(60)</t>
         </is>
       </c>
-      <c r="D45" s="22" t="inlineStr"/>
-      <c r="E45" s="19" t="inlineStr"/>
-      <c r="F45" s="23" t="inlineStr">
+      <c r="D45" s="21" t="inlineStr"/>
+      <c r="E45" s="18" t="inlineStr"/>
+      <c r="F45" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -2780,19 +2739,19 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr"/>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>school</t>
         </is>
       </c>
-      <c r="C46" s="21" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr">
         <is>
           <t>varchar(120)</t>
         </is>
       </c>
-      <c r="D46" s="22" t="inlineStr"/>
-      <c r="E46" s="19" t="inlineStr"/>
-      <c r="F46" s="23" t="inlineStr">
+      <c r="D46" s="21" t="inlineStr"/>
+      <c r="E46" s="18" t="inlineStr"/>
+      <c r="F46" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -2801,27 +2760,27 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr"/>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>branch_id</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D47" s="24" t="inlineStr">
+      <c r="D47" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E47" s="19" t="inlineStr">
+      <c r="E47" s="18" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
       </c>
-      <c r="F47" s="20" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2830,19 +2789,19 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr"/>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="C48" s="21" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>varchar(32)</t>
         </is>
       </c>
-      <c r="D48" s="22" t="inlineStr"/>
-      <c r="E48" s="19" t="inlineStr"/>
-      <c r="F48" s="23" t="inlineStr">
+      <c r="D48" s="21" t="inlineStr"/>
+      <c r="E48" s="18" t="inlineStr"/>
+      <c r="F48" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -2851,19 +2810,19 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr"/>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>funding_percent</t>
         </is>
       </c>
-      <c r="C49" s="21" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>numeric(5,2)</t>
         </is>
       </c>
-      <c r="D49" s="22" t="inlineStr"/>
-      <c r="E49" s="19" t="inlineStr"/>
-      <c r="F49" s="23" t="inlineStr">
+      <c r="D49" s="21" t="inlineStr"/>
+      <c r="E49" s="18" t="inlineStr"/>
+      <c r="F49" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -2876,27 +2835,27 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr"/>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>current_group_id</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D50" s="24" t="inlineStr">
+      <c r="D50" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E50" s="19" t="inlineStr">
+      <c r="E50" s="18" t="inlineStr">
         <is>
           <t>study_group(id)</t>
         </is>
       </c>
-      <c r="F50" s="23" t="inlineStr">
+      <c r="F50" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -2905,27 +2864,27 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr"/>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>intake_id</t>
         </is>
       </c>
-      <c r="C51" s="17" t="inlineStr">
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D51" s="24" t="inlineStr">
+      <c r="D51" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E51" s="19" t="inlineStr">
+      <c r="E51" s="18" t="inlineStr">
         <is>
           <t>intake(id)</t>
         </is>
       </c>
-      <c r="F51" s="23" t="inlineStr">
+      <c r="F51" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -2934,27 +2893,27 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr"/>
-      <c r="B52" s="17" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>age_category_id</t>
         </is>
       </c>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D52" s="24" t="inlineStr">
+      <c r="D52" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E52" s="19" t="inlineStr">
+      <c r="E52" s="18" t="inlineStr">
         <is>
           <t>age_category(id)</t>
         </is>
       </c>
-      <c r="F52" s="23" t="inlineStr">
+      <c r="F52" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -2963,19 +2922,19 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr"/>
-      <c r="B53" s="17" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C53" s="21" t="inlineStr">
+      <c r="C53" s="20" t="inlineStr">
         <is>
           <t>student_status</t>
         </is>
       </c>
-      <c r="D53" s="22" t="inlineStr"/>
-      <c r="E53" s="19" t="inlineStr"/>
-      <c r="F53" s="20" t="inlineStr">
+      <c r="D53" s="21" t="inlineStr"/>
+      <c r="E53" s="18" t="inlineStr"/>
+      <c r="F53" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -2988,27 +2947,27 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr"/>
-      <c r="B54" s="17" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>alumni_category_id</t>
         </is>
       </c>
-      <c r="C54" s="17" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D54" s="24" t="inlineStr">
+      <c r="D54" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E54" s="19" t="inlineStr">
+      <c r="E54" s="18" t="inlineStr">
         <is>
           <t>age_category(id)</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
+      <c r="F54" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3021,19 +2980,19 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr"/>
-      <c r="B55" s="17" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>alumni_year</t>
         </is>
       </c>
-      <c r="C55" s="17" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D55" s="22" t="inlineStr"/>
-      <c r="E55" s="19" t="inlineStr"/>
-      <c r="F55" s="23" t="inlineStr">
+      <c r="D55" s="21" t="inlineStr"/>
+      <c r="E55" s="18" t="inlineStr"/>
+      <c r="F55" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3046,19 +3005,19 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr"/>
-      <c r="B56" s="17" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>waitlisted_on</t>
         </is>
       </c>
-      <c r="C56" s="17" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D56" s="22" t="inlineStr"/>
-      <c r="E56" s="19" t="inlineStr"/>
-      <c r="F56" s="23" t="inlineStr">
+      <c r="D56" s="21" t="inlineStr"/>
+      <c r="E56" s="18" t="inlineStr"/>
+      <c r="F56" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3071,19 +3030,19 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr"/>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t>withdrawn_on</t>
         </is>
       </c>
-      <c r="C57" s="17" t="inlineStr">
+      <c r="C57" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D57" s="22" t="inlineStr"/>
-      <c r="E57" s="19" t="inlineStr"/>
-      <c r="F57" s="23" t="inlineStr">
+      <c r="D57" s="21" t="inlineStr"/>
+      <c r="E57" s="18" t="inlineStr"/>
+      <c r="F57" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3096,19 +3055,19 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr"/>
-      <c r="B58" s="17" t="inlineStr">
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>withdrawal_reason</t>
         </is>
       </c>
-      <c r="C58" s="21" t="inlineStr">
+      <c r="C58" s="20" t="inlineStr">
         <is>
           <t>varchar(120)</t>
         </is>
       </c>
-      <c r="D58" s="22" t="inlineStr"/>
-      <c r="E58" s="19" t="inlineStr"/>
-      <c r="F58" s="23" t="inlineStr">
+      <c r="D58" s="21" t="inlineStr"/>
+      <c r="E58" s="18" t="inlineStr"/>
+      <c r="F58" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3117,19 +3076,19 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr"/>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>graduated_on</t>
         </is>
       </c>
-      <c r="C59" s="17" t="inlineStr">
+      <c r="C59" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D59" s="22" t="inlineStr"/>
-      <c r="E59" s="19" t="inlineStr"/>
-      <c r="F59" s="23" t="inlineStr">
+      <c r="D59" s="21" t="inlineStr"/>
+      <c r="E59" s="18" t="inlineStr"/>
+      <c r="F59" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3142,19 +3101,19 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr"/>
-      <c r="B60" s="17" t="inlineStr">
+      <c r="B60" s="16" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="C60" s="17" t="inlineStr">
+      <c r="C60" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D60" s="22" t="inlineStr"/>
-      <c r="E60" s="19" t="inlineStr"/>
-      <c r="F60" s="23" t="inlineStr">
+      <c r="D60" s="21" t="inlineStr"/>
+      <c r="E60" s="18" t="inlineStr"/>
+      <c r="F60" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3163,19 +3122,19 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr"/>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr">
         <is>
           <t>synced_at</t>
         </is>
       </c>
-      <c r="C61" s="21" t="inlineStr">
+      <c r="C61" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D61" s="22" t="inlineStr"/>
-      <c r="E61" s="19" t="inlineStr"/>
-      <c r="F61" s="23" t="inlineStr">
+      <c r="D61" s="21" t="inlineStr"/>
+      <c r="E61" s="18" t="inlineStr"/>
+      <c r="F61" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3187,37 +3146,37 @@
       </c>
     </row>
     <row r="62" ht="4" customHeight="1">
-      <c r="A62" s="25" t="n"/>
-      <c r="B62" s="25" t="n"/>
-      <c r="C62" s="25" t="n"/>
-      <c r="D62" s="25" t="n"/>
-      <c r="E62" s="25" t="n"/>
-      <c r="F62" s="25" t="n"/>
-      <c r="G62" s="25" t="n"/>
+      <c r="A62" s="24" t="n"/>
+      <c r="B62" s="24" t="n"/>
+      <c r="C62" s="24" t="n"/>
+      <c r="D62" s="24" t="n"/>
+      <c r="E62" s="24" t="n"/>
+      <c r="F62" s="24" t="n"/>
+      <c r="G62" s="24" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="B63" s="16" t="inlineStr">
+      <c r="B63" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C63" s="17" t="inlineStr">
+      <c r="C63" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D63" s="18" t="inlineStr">
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E63" s="19" t="inlineStr"/>
-      <c r="F63" s="20" t="inlineStr">
+      <c r="E63" s="18" t="inlineStr"/>
+      <c r="F63" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3226,27 +3185,27 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr"/>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="C64" s="17" t="inlineStr">
+      <c r="C64" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D64" s="24" t="inlineStr">
+      <c r="D64" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E64" s="19" t="inlineStr">
+      <c r="E64" s="18" t="inlineStr">
         <is>
           <t>app_user(id)</t>
         </is>
       </c>
-      <c r="F64" s="23" t="inlineStr">
+      <c r="F64" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3255,19 +3214,19 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr"/>
-      <c r="B65" s="17" t="inlineStr">
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>personal_id</t>
         </is>
       </c>
-      <c r="C65" s="21" t="inlineStr">
+      <c r="C65" s="20" t="inlineStr">
         <is>
           <t>varchar(11)</t>
         </is>
       </c>
-      <c r="D65" s="22" t="inlineStr"/>
-      <c r="E65" s="19" t="inlineStr"/>
-      <c r="F65" s="23" t="inlineStr">
+      <c r="D65" s="21" t="inlineStr"/>
+      <c r="E65" s="18" t="inlineStr"/>
+      <c r="F65" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3280,19 +3239,19 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr"/>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="C66" s="21" t="inlineStr">
+      <c r="C66" s="20" t="inlineStr">
         <is>
           <t>varchar(120)</t>
         </is>
       </c>
-      <c r="D66" s="22" t="inlineStr"/>
-      <c r="E66" s="19" t="inlineStr"/>
-      <c r="F66" s="20" t="inlineStr">
+      <c r="D66" s="21" t="inlineStr"/>
+      <c r="E66" s="18" t="inlineStr"/>
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3301,19 +3260,19 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr"/>
-      <c r="B67" s="17" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="C67" s="21" t="inlineStr">
+      <c r="C67" s="20" t="inlineStr">
         <is>
           <t>varchar(32)</t>
         </is>
       </c>
-      <c r="D67" s="22" t="inlineStr"/>
-      <c r="E67" s="19" t="inlineStr"/>
-      <c r="F67" s="23" t="inlineStr">
+      <c r="D67" s="21" t="inlineStr"/>
+      <c r="E67" s="18" t="inlineStr"/>
+      <c r="F67" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3322,19 +3281,19 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr"/>
-      <c r="B68" s="17" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="C68" s="21" t="inlineStr">
+      <c r="C68" s="20" t="inlineStr">
         <is>
           <t>varchar(160)</t>
         </is>
       </c>
-      <c r="D68" s="22" t="inlineStr"/>
-      <c r="E68" s="19" t="inlineStr"/>
-      <c r="F68" s="23" t="inlineStr">
+      <c r="D68" s="21" t="inlineStr"/>
+      <c r="E68" s="18" t="inlineStr"/>
+      <c r="F68" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3343,19 +3302,19 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr"/>
-      <c r="B69" s="17" t="inlineStr">
+      <c r="B69" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C69" s="21" t="inlineStr">
+      <c r="C69" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D69" s="22" t="inlineStr"/>
-      <c r="E69" s="19" t="inlineStr"/>
-      <c r="F69" s="20" t="inlineStr">
+      <c r="D69" s="21" t="inlineStr"/>
+      <c r="E69" s="18" t="inlineStr"/>
+      <c r="F69" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3363,37 +3322,37 @@
       <c r="G69" s="4" t="inlineStr"/>
     </row>
     <row r="70" ht="4" customHeight="1">
-      <c r="A70" s="25" t="n"/>
-      <c r="B70" s="25" t="n"/>
-      <c r="C70" s="25" t="n"/>
-      <c r="D70" s="25" t="n"/>
-      <c r="E70" s="25" t="n"/>
-      <c r="F70" s="25" t="n"/>
-      <c r="G70" s="25" t="n"/>
+      <c r="A70" s="24" t="n"/>
+      <c r="B70" s="24" t="n"/>
+      <c r="C70" s="24" t="n"/>
+      <c r="D70" s="24" t="n"/>
+      <c r="E70" s="24" t="n"/>
+      <c r="F70" s="24" t="n"/>
+      <c r="G70" s="24" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="15" t="inlineStr">
+      <c r="A71" s="14" t="inlineStr">
         <is>
           <t>student_parent</t>
         </is>
       </c>
-      <c r="B71" s="16" t="inlineStr">
+      <c r="B71" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C71" s="17" t="inlineStr">
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D71" s="18" t="inlineStr">
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E71" s="19" t="inlineStr"/>
-      <c r="F71" s="20" t="inlineStr">
+      <c r="E71" s="18" t="inlineStr"/>
+      <c r="F71" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3402,27 +3361,27 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr"/>
-      <c r="B72" s="17" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>student_id</t>
         </is>
       </c>
-      <c r="C72" s="17" t="inlineStr">
+      <c r="C72" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D72" s="24" t="inlineStr">
+      <c r="D72" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E72" s="19" t="inlineStr">
+      <c r="E72" s="18" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
       </c>
-      <c r="F72" s="20" t="inlineStr">
+      <c r="F72" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3431,27 +3390,27 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr"/>
-      <c r="B73" s="17" t="inlineStr">
+      <c r="B73" s="16" t="inlineStr">
         <is>
           <t>parent_id</t>
         </is>
       </c>
-      <c r="C73" s="17" t="inlineStr">
+      <c r="C73" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D73" s="24" t="inlineStr">
+      <c r="D73" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E73" s="19" t="inlineStr">
+      <c r="E73" s="18" t="inlineStr">
         <is>
           <t>parent(id)</t>
         </is>
       </c>
-      <c r="F73" s="20" t="inlineStr">
+      <c r="F73" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3460,19 +3419,19 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr"/>
-      <c r="B74" s="17" t="inlineStr">
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>relationship</t>
         </is>
       </c>
-      <c r="C74" s="21" t="inlineStr">
+      <c r="C74" s="20" t="inlineStr">
         <is>
           <t>relationship_type</t>
         </is>
       </c>
-      <c r="D74" s="22" t="inlineStr"/>
-      <c r="E74" s="19" t="inlineStr"/>
-      <c r="F74" s="20" t="inlineStr">
+      <c r="D74" s="21" t="inlineStr"/>
+      <c r="E74" s="18" t="inlineStr"/>
+      <c r="F74" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3485,23 +3444,23 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr"/>
-      <c r="B75" s="17" t="inlineStr">
+      <c r="B75" s="16" t="inlineStr">
         <is>
           <t>uq_student_parent</t>
         </is>
       </c>
-      <c r="C75" s="17" t="inlineStr">
+      <c r="C75" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D75" s="26" t="inlineStr">
+      <c r="D75" s="25" t="inlineStr">
         <is>
           <t>UQ</t>
         </is>
       </c>
-      <c r="E75" s="19" t="inlineStr"/>
-      <c r="F75" s="23" t="inlineStr"/>
+      <c r="E75" s="18" t="inlineStr"/>
+      <c r="F75" s="22" t="inlineStr"/>
       <c r="G75" s="4" t="inlineStr">
         <is>
           <t>UNIQUE(student_id, parent_id)</t>
@@ -3509,37 +3468,37 @@
       </c>
     </row>
     <row r="76" ht="4" customHeight="1">
-      <c r="A76" s="25" t="n"/>
-      <c r="B76" s="25" t="n"/>
-      <c r="C76" s="25" t="n"/>
-      <c r="D76" s="25" t="n"/>
-      <c r="E76" s="25" t="n"/>
-      <c r="F76" s="25" t="n"/>
-      <c r="G76" s="25" t="n"/>
+      <c r="A76" s="24" t="n"/>
+      <c r="B76" s="24" t="n"/>
+      <c r="C76" s="24" t="n"/>
+      <c r="D76" s="24" t="n"/>
+      <c r="E76" s="24" t="n"/>
+      <c r="F76" s="24" t="n"/>
+      <c r="G76" s="24" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="15" t="inlineStr">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>trainer</t>
         </is>
       </c>
-      <c r="B77" s="16" t="inlineStr">
+      <c r="B77" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C77" s="17" t="inlineStr">
+      <c r="C77" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D77" s="18" t="inlineStr">
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E77" s="19" t="inlineStr"/>
-      <c r="F77" s="20" t="inlineStr">
+      <c r="E77" s="18" t="inlineStr"/>
+      <c r="F77" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3548,27 +3507,27 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr"/>
-      <c r="B78" s="17" t="inlineStr">
+      <c r="B78" s="16" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="C78" s="17" t="inlineStr">
+      <c r="C78" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D78" s="24" t="inlineStr">
+      <c r="D78" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E78" s="19" t="inlineStr">
+      <c r="E78" s="18" t="inlineStr">
         <is>
           <t>app_user(id)</t>
         </is>
       </c>
-      <c r="F78" s="23" t="inlineStr">
+      <c r="F78" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3577,19 +3536,19 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr"/>
-      <c r="B79" s="17" t="inlineStr">
+      <c r="B79" s="16" t="inlineStr">
         <is>
           <t>personal_id</t>
         </is>
       </c>
-      <c r="C79" s="21" t="inlineStr">
+      <c r="C79" s="20" t="inlineStr">
         <is>
           <t>varchar(11)</t>
         </is>
       </c>
-      <c r="D79" s="22" t="inlineStr"/>
-      <c r="E79" s="19" t="inlineStr"/>
-      <c r="F79" s="23" t="inlineStr">
+      <c r="D79" s="21" t="inlineStr"/>
+      <c r="E79" s="18" t="inlineStr"/>
+      <c r="F79" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3602,19 +3561,19 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr"/>
-      <c r="B80" s="17" t="inlineStr">
+      <c r="B80" s="16" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="C80" s="21" t="inlineStr">
+      <c r="C80" s="20" t="inlineStr">
         <is>
           <t>varchar(120)</t>
         </is>
       </c>
-      <c r="D80" s="22" t="inlineStr"/>
-      <c r="E80" s="19" t="inlineStr"/>
-      <c r="F80" s="20" t="inlineStr">
+      <c r="D80" s="21" t="inlineStr"/>
+      <c r="E80" s="18" t="inlineStr"/>
+      <c r="F80" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3623,19 +3582,19 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr"/>
-      <c r="B81" s="17" t="inlineStr">
+      <c r="B81" s="16" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="C81" s="21" t="inlineStr">
+      <c r="C81" s="20" t="inlineStr">
         <is>
           <t>varchar(32)</t>
         </is>
       </c>
-      <c r="D81" s="22" t="inlineStr"/>
-      <c r="E81" s="19" t="inlineStr"/>
-      <c r="F81" s="23" t="inlineStr">
+      <c r="D81" s="21" t="inlineStr"/>
+      <c r="E81" s="18" t="inlineStr"/>
+      <c r="F81" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3644,19 +3603,19 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr"/>
-      <c r="B82" s="17" t="inlineStr">
+      <c r="B82" s="16" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="C82" s="21" t="inlineStr">
+      <c r="C82" s="20" t="inlineStr">
         <is>
           <t>varchar(160)</t>
         </is>
       </c>
-      <c r="D82" s="22" t="inlineStr"/>
-      <c r="E82" s="19" t="inlineStr"/>
-      <c r="F82" s="23" t="inlineStr">
+      <c r="D82" s="21" t="inlineStr"/>
+      <c r="E82" s="18" t="inlineStr"/>
+      <c r="F82" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3665,27 +3624,27 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr"/>
-      <c r="B83" s="17" t="inlineStr">
+      <c r="B83" s="16" t="inlineStr">
         <is>
           <t>branch_id</t>
         </is>
       </c>
-      <c r="C83" s="17" t="inlineStr">
+      <c r="C83" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D83" s="24" t="inlineStr">
+      <c r="D83" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E83" s="19" t="inlineStr">
+      <c r="E83" s="18" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
       </c>
-      <c r="F83" s="23" t="inlineStr">
+      <c r="F83" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3694,19 +3653,19 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr"/>
-      <c r="B84" s="17" t="inlineStr">
+      <c r="B84" s="16" t="inlineStr">
         <is>
           <t>specialization</t>
         </is>
       </c>
-      <c r="C84" s="21" t="inlineStr">
+      <c r="C84" s="20" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="D84" s="22" t="inlineStr"/>
-      <c r="E84" s="19" t="inlineStr"/>
-      <c r="F84" s="23" t="inlineStr">
+      <c r="D84" s="21" t="inlineStr"/>
+      <c r="E84" s="18" t="inlineStr"/>
+      <c r="F84" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3719,19 +3678,19 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr"/>
-      <c r="B85" s="17" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
         <is>
           <t>qualification</t>
         </is>
       </c>
-      <c r="C85" s="17" t="inlineStr">
+      <c r="C85" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D85" s="22" t="inlineStr"/>
-      <c r="E85" s="19" t="inlineStr"/>
-      <c r="F85" s="23" t="inlineStr">
+      <c r="D85" s="21" t="inlineStr"/>
+      <c r="E85" s="18" t="inlineStr"/>
+      <c r="F85" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3744,19 +3703,19 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr"/>
-      <c r="B86" s="17" t="inlineStr">
+      <c r="B86" s="16" t="inlineStr">
         <is>
           <t>certificates</t>
         </is>
       </c>
-      <c r="C86" s="21" t="inlineStr">
+      <c r="C86" s="20" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="D86" s="22" t="inlineStr"/>
-      <c r="E86" s="19" t="inlineStr"/>
-      <c r="F86" s="23" t="inlineStr">
+      <c r="D86" s="21" t="inlineStr"/>
+      <c r="E86" s="18" t="inlineStr"/>
+      <c r="F86" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3765,19 +3724,19 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr"/>
-      <c r="B87" s="17" t="inlineStr">
+      <c r="B87" s="16" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="C87" s="21" t="inlineStr">
+      <c r="C87" s="20" t="inlineStr">
         <is>
           <t>numeric(2,1)</t>
         </is>
       </c>
-      <c r="D87" s="22" t="inlineStr"/>
-      <c r="E87" s="19" t="inlineStr"/>
-      <c r="F87" s="23" t="inlineStr">
+      <c r="D87" s="21" t="inlineStr"/>
+      <c r="E87" s="18" t="inlineStr"/>
+      <c r="F87" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3790,19 +3749,19 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr"/>
-      <c r="B88" s="17" t="inlineStr">
+      <c r="B88" s="16" t="inlineStr">
         <is>
           <t>work_started_on</t>
         </is>
       </c>
-      <c r="C88" s="17" t="inlineStr">
+      <c r="C88" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D88" s="22" t="inlineStr"/>
-      <c r="E88" s="19" t="inlineStr"/>
-      <c r="F88" s="23" t="inlineStr">
+      <c r="D88" s="21" t="inlineStr"/>
+      <c r="E88" s="18" t="inlineStr"/>
+      <c r="F88" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3815,19 +3774,19 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr"/>
-      <c r="B89" s="17" t="inlineStr">
+      <c r="B89" s="16" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
       </c>
-      <c r="C89" s="17" t="inlineStr">
+      <c r="C89" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="D89" s="22" t="inlineStr"/>
-      <c r="E89" s="19" t="inlineStr"/>
-      <c r="F89" s="20" t="inlineStr">
+      <c r="D89" s="21" t="inlineStr"/>
+      <c r="E89" s="18" t="inlineStr"/>
+      <c r="F89" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3836,19 +3795,19 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr"/>
-      <c r="B90" s="17" t="inlineStr">
+      <c r="B90" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C90" s="21" t="inlineStr">
+      <c r="C90" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D90" s="22" t="inlineStr"/>
-      <c r="E90" s="19" t="inlineStr"/>
-      <c r="F90" s="20" t="inlineStr">
+      <c r="D90" s="21" t="inlineStr"/>
+      <c r="E90" s="18" t="inlineStr"/>
+      <c r="F90" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3856,37 +3815,37 @@
       <c r="G90" s="4" t="inlineStr"/>
     </row>
     <row r="91" ht="4" customHeight="1">
-      <c r="A91" s="25" t="n"/>
-      <c r="B91" s="25" t="n"/>
-      <c r="C91" s="25" t="n"/>
-      <c r="D91" s="25" t="n"/>
-      <c r="E91" s="25" t="n"/>
-      <c r="F91" s="25" t="n"/>
-      <c r="G91" s="25" t="n"/>
+      <c r="A91" s="24" t="n"/>
+      <c r="B91" s="24" t="n"/>
+      <c r="C91" s="24" t="n"/>
+      <c r="D91" s="24" t="n"/>
+      <c r="E91" s="24" t="n"/>
+      <c r="F91" s="24" t="n"/>
+      <c r="G91" s="24" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="15" t="inlineStr">
+      <c r="A92" s="14" t="inlineStr">
         <is>
           <t>staff_member</t>
         </is>
       </c>
-      <c r="B92" s="16" t="inlineStr">
+      <c r="B92" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C92" s="17" t="inlineStr">
+      <c r="C92" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D92" s="18" t="inlineStr">
+      <c r="D92" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E92" s="19" t="inlineStr"/>
-      <c r="F92" s="20" t="inlineStr">
+      <c r="E92" s="18" t="inlineStr"/>
+      <c r="F92" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3895,27 +3854,27 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr"/>
-      <c r="B93" s="17" t="inlineStr">
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="C93" s="17" t="inlineStr">
+      <c r="C93" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D93" s="24" t="inlineStr">
+      <c r="D93" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E93" s="19" t="inlineStr">
+      <c r="E93" s="18" t="inlineStr">
         <is>
           <t>app_user(id)</t>
         </is>
       </c>
-      <c r="F93" s="20" t="inlineStr">
+      <c r="F93" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3924,19 +3883,19 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr"/>
-      <c r="B94" s="17" t="inlineStr">
+      <c r="B94" s="16" t="inlineStr">
         <is>
           <t>personal_id</t>
         </is>
       </c>
-      <c r="C94" s="21" t="inlineStr">
+      <c r="C94" s="20" t="inlineStr">
         <is>
           <t>varchar(11)</t>
         </is>
       </c>
-      <c r="D94" s="22" t="inlineStr"/>
-      <c r="E94" s="19" t="inlineStr"/>
-      <c r="F94" s="23" t="inlineStr">
+      <c r="D94" s="21" t="inlineStr"/>
+      <c r="E94" s="18" t="inlineStr"/>
+      <c r="F94" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3949,19 +3908,19 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr"/>
-      <c r="B95" s="17" t="inlineStr">
+      <c r="B95" s="16" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="C95" s="21" t="inlineStr">
+      <c r="C95" s="20" t="inlineStr">
         <is>
           <t>varchar(120)</t>
         </is>
       </c>
-      <c r="D95" s="22" t="inlineStr"/>
-      <c r="E95" s="19" t="inlineStr"/>
-      <c r="F95" s="20" t="inlineStr">
+      <c r="D95" s="21" t="inlineStr"/>
+      <c r="E95" s="18" t="inlineStr"/>
+      <c r="F95" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -3970,19 +3929,19 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr"/>
-      <c r="B96" s="17" t="inlineStr">
+      <c r="B96" s="16" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="C96" s="21" t="inlineStr">
+      <c r="C96" s="20" t="inlineStr">
         <is>
           <t>varchar(32)</t>
         </is>
       </c>
-      <c r="D96" s="22" t="inlineStr"/>
-      <c r="E96" s="19" t="inlineStr"/>
-      <c r="F96" s="23" t="inlineStr">
+      <c r="D96" s="21" t="inlineStr"/>
+      <c r="E96" s="18" t="inlineStr"/>
+      <c r="F96" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -3991,19 +3950,19 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr"/>
-      <c r="B97" s="17" t="inlineStr">
+      <c r="B97" s="16" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="C97" s="21" t="inlineStr">
+      <c r="C97" s="20" t="inlineStr">
         <is>
           <t>varchar(160)</t>
         </is>
       </c>
-      <c r="D97" s="22" t="inlineStr"/>
-      <c r="E97" s="19" t="inlineStr"/>
-      <c r="F97" s="23" t="inlineStr">
+      <c r="D97" s="21" t="inlineStr"/>
+      <c r="E97" s="18" t="inlineStr"/>
+      <c r="F97" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -4012,19 +3971,19 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr"/>
-      <c r="B98" s="17" t="inlineStr">
+      <c r="B98" s="16" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="C98" s="21" t="inlineStr">
+      <c r="C98" s="20" t="inlineStr">
         <is>
           <t>user_role</t>
         </is>
       </c>
-      <c r="D98" s="22" t="inlineStr"/>
-      <c r="E98" s="19" t="inlineStr"/>
-      <c r="F98" s="20" t="inlineStr">
+      <c r="D98" s="21" t="inlineStr"/>
+      <c r="E98" s="18" t="inlineStr"/>
+      <c r="F98" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4037,27 +3996,27 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr"/>
-      <c r="B99" s="17" t="inlineStr">
+      <c r="B99" s="16" t="inlineStr">
         <is>
           <t>branch_id</t>
         </is>
       </c>
-      <c r="C99" s="17" t="inlineStr">
+      <c r="C99" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D99" s="24" t="inlineStr">
+      <c r="D99" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E99" s="19" t="inlineStr">
+      <c r="E99" s="18" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
       </c>
-      <c r="F99" s="23" t="inlineStr">
+      <c r="F99" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -4070,19 +4029,19 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr"/>
-      <c r="B100" s="17" t="inlineStr">
+      <c r="B100" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C100" s="21" t="inlineStr">
+      <c r="C100" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D100" s="22" t="inlineStr"/>
-      <c r="E100" s="19" t="inlineStr"/>
-      <c r="F100" s="20" t="inlineStr">
+      <c r="D100" s="21" t="inlineStr"/>
+      <c r="E100" s="18" t="inlineStr"/>
+      <c r="F100" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4090,37 +4049,37 @@
       <c r="G100" s="4" t="inlineStr"/>
     </row>
     <row r="101" ht="4" customHeight="1">
-      <c r="A101" s="25" t="n"/>
-      <c r="B101" s="25" t="n"/>
-      <c r="C101" s="25" t="n"/>
-      <c r="D101" s="25" t="n"/>
-      <c r="E101" s="25" t="n"/>
-      <c r="F101" s="25" t="n"/>
-      <c r="G101" s="25" t="n"/>
+      <c r="A101" s="24" t="n"/>
+      <c r="B101" s="24" t="n"/>
+      <c r="C101" s="24" t="n"/>
+      <c r="D101" s="24" t="n"/>
+      <c r="E101" s="24" t="n"/>
+      <c r="F101" s="24" t="n"/>
+      <c r="G101" s="24" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="15" t="inlineStr">
+      <c r="A102" s="14" t="inlineStr">
         <is>
           <t>study_group</t>
         </is>
       </c>
-      <c r="B102" s="16" t="inlineStr">
+      <c r="B102" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C102" s="17" t="inlineStr">
+      <c r="C102" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D102" s="18" t="inlineStr">
+      <c r="D102" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E102" s="19" t="inlineStr"/>
-      <c r="F102" s="20" t="inlineStr">
+      <c r="E102" s="18" t="inlineStr"/>
+      <c r="F102" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4129,23 +4088,23 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr"/>
-      <c r="B103" s="17" t="inlineStr">
+      <c r="B103" s="16" t="inlineStr">
         <is>
           <t>group_number</t>
         </is>
       </c>
-      <c r="C103" s="21" t="inlineStr">
+      <c r="C103" s="20" t="inlineStr">
         <is>
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="D103" s="26" t="inlineStr">
+      <c r="D103" s="25" t="inlineStr">
         <is>
           <t>UQ</t>
         </is>
       </c>
-      <c r="E103" s="19" t="inlineStr"/>
-      <c r="F103" s="20" t="inlineStr">
+      <c r="E103" s="18" t="inlineStr"/>
+      <c r="F103" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4158,27 +4117,27 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr"/>
-      <c r="B104" s="17" t="inlineStr">
+      <c r="B104" s="16" t="inlineStr">
         <is>
           <t>branch_id</t>
         </is>
       </c>
-      <c r="C104" s="17" t="inlineStr">
+      <c r="C104" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D104" s="24" t="inlineStr">
+      <c r="D104" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E104" s="19" t="inlineStr">
+      <c r="E104" s="18" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
       </c>
-      <c r="F104" s="20" t="inlineStr">
+      <c r="F104" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4187,27 +4146,27 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr"/>
-      <c r="B105" s="17" t="inlineStr">
+      <c r="B105" s="16" t="inlineStr">
         <is>
           <t>age_category_id</t>
         </is>
       </c>
-      <c r="C105" s="17" t="inlineStr">
+      <c r="C105" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D105" s="24" t="inlineStr">
+      <c r="D105" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E105" s="19" t="inlineStr">
+      <c r="E105" s="18" t="inlineStr">
         <is>
           <t>age_category(id)</t>
         </is>
       </c>
-      <c r="F105" s="20" t="inlineStr">
+      <c r="F105" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4216,27 +4175,27 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr"/>
-      <c r="B106" s="17" t="inlineStr">
+      <c r="B106" s="16" t="inlineStr">
         <is>
           <t>intake_id</t>
         </is>
       </c>
-      <c r="C106" s="17" t="inlineStr">
+      <c r="C106" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D106" s="24" t="inlineStr">
+      <c r="D106" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E106" s="19" t="inlineStr">
+      <c r="E106" s="18" t="inlineStr">
         <is>
           <t>intake(id)</t>
         </is>
       </c>
-      <c r="F106" s="20" t="inlineStr">
+      <c r="F106" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4245,27 +4204,27 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr"/>
-      <c r="B107" s="17" t="inlineStr">
+      <c r="B107" s="16" t="inlineStr">
         <is>
           <t>module_id</t>
         </is>
       </c>
-      <c r="C107" s="17" t="inlineStr">
+      <c r="C107" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D107" s="24" t="inlineStr">
+      <c r="D107" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E107" s="19" t="inlineStr">
+      <c r="E107" s="18" t="inlineStr">
         <is>
           <t>module(id)</t>
         </is>
       </c>
-      <c r="F107" s="23" t="inlineStr">
+      <c r="F107" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -4278,19 +4237,19 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr"/>
-      <c r="B108" s="17" t="inlineStr">
+      <c r="B108" s="16" t="inlineStr">
         <is>
           <t>current_semester_no</t>
         </is>
       </c>
-      <c r="C108" s="17" t="inlineStr">
+      <c r="C108" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D108" s="22" t="inlineStr"/>
-      <c r="E108" s="19" t="inlineStr"/>
-      <c r="F108" s="20" t="inlineStr">
+      <c r="D108" s="21" t="inlineStr"/>
+      <c r="E108" s="18" t="inlineStr"/>
+      <c r="F108" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4303,19 +4262,19 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr"/>
-      <c r="B109" s="17" t="inlineStr">
+      <c r="B109" s="16" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C109" s="21" t="inlineStr">
+      <c r="C109" s="20" t="inlineStr">
         <is>
           <t>group_status</t>
         </is>
       </c>
-      <c r="D109" s="22" t="inlineStr"/>
-      <c r="E109" s="19" t="inlineStr"/>
-      <c r="F109" s="20" t="inlineStr">
+      <c r="D109" s="21" t="inlineStr"/>
+      <c r="E109" s="18" t="inlineStr"/>
+      <c r="F109" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4328,19 +4287,19 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr"/>
-      <c r="B110" s="17" t="inlineStr">
+      <c r="B110" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C110" s="21" t="inlineStr">
+      <c r="C110" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D110" s="22" t="inlineStr"/>
-      <c r="E110" s="19" t="inlineStr"/>
-      <c r="F110" s="20" t="inlineStr">
+      <c r="D110" s="21" t="inlineStr"/>
+      <c r="E110" s="18" t="inlineStr"/>
+      <c r="F110" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4348,37 +4307,37 @@
       <c r="G110" s="4" t="inlineStr"/>
     </row>
     <row r="111" ht="4" customHeight="1">
-      <c r="A111" s="25" t="n"/>
-      <c r="B111" s="25" t="n"/>
-      <c r="C111" s="25" t="n"/>
-      <c r="D111" s="25" t="n"/>
-      <c r="E111" s="25" t="n"/>
-      <c r="F111" s="25" t="n"/>
-      <c r="G111" s="25" t="n"/>
+      <c r="A111" s="24" t="n"/>
+      <c r="B111" s="24" t="n"/>
+      <c r="C111" s="24" t="n"/>
+      <c r="D111" s="24" t="n"/>
+      <c r="E111" s="24" t="n"/>
+      <c r="F111" s="24" t="n"/>
+      <c r="G111" s="24" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="15" t="inlineStr">
+      <c r="A112" s="14" t="inlineStr">
         <is>
           <t>group_membership</t>
         </is>
       </c>
-      <c r="B112" s="16" t="inlineStr">
+      <c r="B112" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C112" s="17" t="inlineStr">
+      <c r="C112" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D112" s="18" t="inlineStr">
+      <c r="D112" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E112" s="19" t="inlineStr"/>
-      <c r="F112" s="20" t="inlineStr">
+      <c r="E112" s="18" t="inlineStr"/>
+      <c r="F112" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4387,27 +4346,27 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr"/>
-      <c r="B113" s="17" t="inlineStr">
+      <c r="B113" s="16" t="inlineStr">
         <is>
           <t>group_id</t>
         </is>
       </c>
-      <c r="C113" s="17" t="inlineStr">
+      <c r="C113" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D113" s="24" t="inlineStr">
+      <c r="D113" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E113" s="19" t="inlineStr">
+      <c r="E113" s="18" t="inlineStr">
         <is>
           <t>study_group(id)</t>
         </is>
       </c>
-      <c r="F113" s="20" t="inlineStr">
+      <c r="F113" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4416,27 +4375,27 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr"/>
-      <c r="B114" s="17" t="inlineStr">
+      <c r="B114" s="16" t="inlineStr">
         <is>
           <t>student_id</t>
         </is>
       </c>
-      <c r="C114" s="17" t="inlineStr">
+      <c r="C114" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D114" s="24" t="inlineStr">
+      <c r="D114" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E114" s="19" t="inlineStr">
+      <c r="E114" s="18" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
       </c>
-      <c r="F114" s="20" t="inlineStr">
+      <c r="F114" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4445,19 +4404,19 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr"/>
-      <c r="B115" s="17" t="inlineStr">
+      <c r="B115" s="16" t="inlineStr">
         <is>
           <t>joined_on</t>
         </is>
       </c>
-      <c r="C115" s="17" t="inlineStr">
+      <c r="C115" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D115" s="22" t="inlineStr"/>
-      <c r="E115" s="19" t="inlineStr"/>
-      <c r="F115" s="20" t="inlineStr">
+      <c r="D115" s="21" t="inlineStr"/>
+      <c r="E115" s="18" t="inlineStr"/>
+      <c r="F115" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4466,19 +4425,19 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr"/>
-      <c r="B116" s="17" t="inlineStr">
+      <c r="B116" s="16" t="inlineStr">
         <is>
           <t>left_on</t>
         </is>
       </c>
-      <c r="C116" s="17" t="inlineStr">
+      <c r="C116" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D116" s="22" t="inlineStr"/>
-      <c r="E116" s="19" t="inlineStr"/>
-      <c r="F116" s="23" t="inlineStr">
+      <c r="D116" s="21" t="inlineStr"/>
+      <c r="E116" s="18" t="inlineStr"/>
+      <c r="F116" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -4487,19 +4446,19 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr"/>
-      <c r="B117" s="17" t="inlineStr">
+      <c r="B117" s="16" t="inlineStr">
         <is>
           <t>leave_reason</t>
         </is>
       </c>
-      <c r="C117" s="21" t="inlineStr">
+      <c r="C117" s="20" t="inlineStr">
         <is>
           <t>varchar(120)</t>
         </is>
       </c>
-      <c r="D117" s="22" t="inlineStr"/>
-      <c r="E117" s="19" t="inlineStr"/>
-      <c r="F117" s="23" t="inlineStr">
+      <c r="D117" s="21" t="inlineStr"/>
+      <c r="E117" s="18" t="inlineStr"/>
+      <c r="F117" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -4512,19 +4471,19 @@
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr"/>
-      <c r="B118" s="17" t="inlineStr">
+      <c r="B118" s="16" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
       </c>
-      <c r="C118" s="17" t="inlineStr">
+      <c r="C118" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="D118" s="22" t="inlineStr"/>
-      <c r="E118" s="19" t="inlineStr"/>
-      <c r="F118" s="20" t="inlineStr">
+      <c r="D118" s="21" t="inlineStr"/>
+      <c r="E118" s="18" t="inlineStr"/>
+      <c r="F118" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4532,37 +4491,37 @@
       <c r="G118" s="4" t="inlineStr"/>
     </row>
     <row r="119" ht="4" customHeight="1">
-      <c r="A119" s="25" t="n"/>
-      <c r="B119" s="25" t="n"/>
-      <c r="C119" s="25" t="n"/>
-      <c r="D119" s="25" t="n"/>
-      <c r="E119" s="25" t="n"/>
-      <c r="F119" s="25" t="n"/>
-      <c r="G119" s="25" t="n"/>
+      <c r="A119" s="24" t="n"/>
+      <c r="B119" s="24" t="n"/>
+      <c r="C119" s="24" t="n"/>
+      <c r="D119" s="24" t="n"/>
+      <c r="E119" s="24" t="n"/>
+      <c r="F119" s="24" t="n"/>
+      <c r="G119" s="24" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="15" t="inlineStr">
+      <c r="A120" s="14" t="inlineStr">
         <is>
           <t>module_template</t>
         </is>
       </c>
-      <c r="B120" s="16" t="inlineStr">
+      <c r="B120" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C120" s="17" t="inlineStr">
+      <c r="C120" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D120" s="18" t="inlineStr">
+      <c r="D120" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E120" s="19" t="inlineStr"/>
-      <c r="F120" s="20" t="inlineStr">
+      <c r="E120" s="18" t="inlineStr"/>
+      <c r="F120" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4571,27 +4530,27 @@
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr"/>
-      <c r="B121" s="17" t="inlineStr">
+      <c r="B121" s="16" t="inlineStr">
         <is>
           <t>age_category_id</t>
         </is>
       </c>
-      <c r="C121" s="17" t="inlineStr">
+      <c r="C121" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D121" s="24" t="inlineStr">
+      <c r="D121" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E121" s="19" t="inlineStr">
+      <c r="E121" s="18" t="inlineStr">
         <is>
           <t>age_category(id)</t>
         </is>
       </c>
-      <c r="F121" s="20" t="inlineStr">
+      <c r="F121" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4600,19 +4559,19 @@
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr"/>
-      <c r="B122" s="17" t="inlineStr">
+      <c r="B122" s="16" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C122" s="21" t="inlineStr">
+      <c r="C122" s="20" t="inlineStr">
         <is>
           <t>varchar(120)</t>
         </is>
       </c>
-      <c r="D122" s="22" t="inlineStr"/>
-      <c r="E122" s="19" t="inlineStr"/>
-      <c r="F122" s="20" t="inlineStr">
+      <c r="D122" s="21" t="inlineStr"/>
+      <c r="E122" s="18" t="inlineStr"/>
+      <c r="F122" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4621,19 +4580,19 @@
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr"/>
-      <c r="B123" s="17" t="inlineStr">
+      <c r="B123" s="16" t="inlineStr">
         <is>
           <t>total_semesters</t>
         </is>
       </c>
-      <c r="C123" s="17" t="inlineStr">
+      <c r="C123" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D123" s="22" t="inlineStr"/>
-      <c r="E123" s="19" t="inlineStr"/>
-      <c r="F123" s="20" t="inlineStr">
+      <c r="D123" s="21" t="inlineStr"/>
+      <c r="E123" s="18" t="inlineStr"/>
+      <c r="F123" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4642,19 +4601,19 @@
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr"/>
-      <c r="B124" s="17" t="inlineStr">
+      <c r="B124" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C124" s="21" t="inlineStr">
+      <c r="C124" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D124" s="22" t="inlineStr"/>
-      <c r="E124" s="19" t="inlineStr"/>
-      <c r="F124" s="20" t="inlineStr">
+      <c r="D124" s="21" t="inlineStr"/>
+      <c r="E124" s="18" t="inlineStr"/>
+      <c r="F124" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4662,37 +4621,37 @@
       <c r="G124" s="4" t="inlineStr"/>
     </row>
     <row r="125" ht="4" customHeight="1">
-      <c r="A125" s="25" t="n"/>
-      <c r="B125" s="25" t="n"/>
-      <c r="C125" s="25" t="n"/>
-      <c r="D125" s="25" t="n"/>
-      <c r="E125" s="25" t="n"/>
-      <c r="F125" s="25" t="n"/>
-      <c r="G125" s="25" t="n"/>
+      <c r="A125" s="24" t="n"/>
+      <c r="B125" s="24" t="n"/>
+      <c r="C125" s="24" t="n"/>
+      <c r="D125" s="24" t="n"/>
+      <c r="E125" s="24" t="n"/>
+      <c r="F125" s="24" t="n"/>
+      <c r="G125" s="24" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="15" t="inlineStr">
+      <c r="A126" s="14" t="inlineStr">
         <is>
           <t>template_lecture</t>
         </is>
       </c>
-      <c r="B126" s="16" t="inlineStr">
+      <c r="B126" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C126" s="17" t="inlineStr">
+      <c r="C126" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D126" s="18" t="inlineStr">
+      <c r="D126" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E126" s="19" t="inlineStr"/>
-      <c r="F126" s="20" t="inlineStr">
+      <c r="E126" s="18" t="inlineStr"/>
+      <c r="F126" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4701,27 +4660,27 @@
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr"/>
-      <c r="B127" s="17" t="inlineStr">
+      <c r="B127" s="16" t="inlineStr">
         <is>
           <t>template_id</t>
         </is>
       </c>
-      <c r="C127" s="17" t="inlineStr">
+      <c r="C127" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D127" s="24" t="inlineStr">
+      <c r="D127" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E127" s="19" t="inlineStr">
+      <c r="E127" s="18" t="inlineStr">
         <is>
           <t>module_template(id)</t>
         </is>
       </c>
-      <c r="F127" s="20" t="inlineStr">
+      <c r="F127" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4730,19 +4689,19 @@
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr"/>
-      <c r="B128" s="17" t="inlineStr">
+      <c r="B128" s="16" t="inlineStr">
         <is>
           <t>semester_no</t>
         </is>
       </c>
-      <c r="C128" s="17" t="inlineStr">
+      <c r="C128" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D128" s="22" t="inlineStr"/>
-      <c r="E128" s="19" t="inlineStr"/>
-      <c r="F128" s="20" t="inlineStr">
+      <c r="D128" s="21" t="inlineStr"/>
+      <c r="E128" s="18" t="inlineStr"/>
+      <c r="F128" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4751,19 +4710,19 @@
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr"/>
-      <c r="B129" s="17" t="inlineStr">
+      <c r="B129" s="16" t="inlineStr">
         <is>
           <t>sequence_no</t>
         </is>
       </c>
-      <c r="C129" s="17" t="inlineStr">
+      <c r="C129" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D129" s="22" t="inlineStr"/>
-      <c r="E129" s="19" t="inlineStr"/>
-      <c r="F129" s="20" t="inlineStr">
+      <c r="D129" s="21" t="inlineStr"/>
+      <c r="E129" s="18" t="inlineStr"/>
+      <c r="F129" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4772,19 +4731,19 @@
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr"/>
-      <c r="B130" s="17" t="inlineStr">
+      <c r="B130" s="16" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C130" s="21" t="inlineStr">
+      <c r="C130" s="20" t="inlineStr">
         <is>
           <t>varchar(160)</t>
         </is>
       </c>
-      <c r="D130" s="22" t="inlineStr"/>
-      <c r="E130" s="19" t="inlineStr"/>
-      <c r="F130" s="20" t="inlineStr">
+      <c r="D130" s="21" t="inlineStr"/>
+      <c r="E130" s="18" t="inlineStr"/>
+      <c r="F130" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4793,19 +4752,19 @@
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr"/>
-      <c r="B131" s="17" t="inlineStr">
+      <c r="B131" s="16" t="inlineStr">
         <is>
           <t>lecture_type</t>
         </is>
       </c>
-      <c r="C131" s="21" t="inlineStr">
+      <c r="C131" s="20" t="inlineStr">
         <is>
           <t>lecture_type</t>
         </is>
       </c>
-      <c r="D131" s="22" t="inlineStr"/>
-      <c r="E131" s="19" t="inlineStr"/>
-      <c r="F131" s="20" t="inlineStr">
+      <c r="D131" s="21" t="inlineStr"/>
+      <c r="E131" s="18" t="inlineStr"/>
+      <c r="F131" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4818,19 +4777,19 @@
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr"/>
-      <c r="B132" s="17" t="inlineStr">
+      <c r="B132" s="16" t="inlineStr">
         <is>
           <t>duration_min</t>
         </is>
       </c>
-      <c r="C132" s="17" t="inlineStr">
+      <c r="C132" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D132" s="22" t="inlineStr"/>
-      <c r="E132" s="19" t="inlineStr"/>
-      <c r="F132" s="23" t="inlineStr">
+      <c r="D132" s="21" t="inlineStr"/>
+      <c r="E132" s="18" t="inlineStr"/>
+      <c r="F132" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -4838,37 +4797,37 @@
       <c r="G132" s="4" t="inlineStr"/>
     </row>
     <row r="133" ht="4" customHeight="1">
-      <c r="A133" s="25" t="n"/>
-      <c r="B133" s="25" t="n"/>
-      <c r="C133" s="25" t="n"/>
-      <c r="D133" s="25" t="n"/>
-      <c r="E133" s="25" t="n"/>
-      <c r="F133" s="25" t="n"/>
-      <c r="G133" s="25" t="n"/>
+      <c r="A133" s="24" t="n"/>
+      <c r="B133" s="24" t="n"/>
+      <c r="C133" s="24" t="n"/>
+      <c r="D133" s="24" t="n"/>
+      <c r="E133" s="24" t="n"/>
+      <c r="F133" s="24" t="n"/>
+      <c r="G133" s="24" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="15" t="inlineStr">
+      <c r="A134" s="14" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="B134" s="16" t="inlineStr">
+      <c r="B134" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C134" s="17" t="inlineStr">
+      <c r="C134" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D134" s="18" t="inlineStr">
+      <c r="D134" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E134" s="19" t="inlineStr"/>
-      <c r="F134" s="20" t="inlineStr">
+      <c r="E134" s="18" t="inlineStr"/>
+      <c r="F134" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4877,27 +4836,27 @@
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr"/>
-      <c r="B135" s="17" t="inlineStr">
+      <c r="B135" s="16" t="inlineStr">
         <is>
           <t>intake_id</t>
         </is>
       </c>
-      <c r="C135" s="17" t="inlineStr">
+      <c r="C135" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D135" s="24" t="inlineStr">
+      <c r="D135" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E135" s="19" t="inlineStr">
+      <c r="E135" s="18" t="inlineStr">
         <is>
           <t>intake(id)</t>
         </is>
       </c>
-      <c r="F135" s="20" t="inlineStr">
+      <c r="F135" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4906,27 +4865,27 @@
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr"/>
-      <c r="B136" s="17" t="inlineStr">
+      <c r="B136" s="16" t="inlineStr">
         <is>
           <t>age_category_id</t>
         </is>
       </c>
-      <c r="C136" s="17" t="inlineStr">
+      <c r="C136" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D136" s="24" t="inlineStr">
+      <c r="D136" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E136" s="19" t="inlineStr">
+      <c r="E136" s="18" t="inlineStr">
         <is>
           <t>age_category(id)</t>
         </is>
       </c>
-      <c r="F136" s="20" t="inlineStr">
+      <c r="F136" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4935,27 +4894,27 @@
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr"/>
-      <c r="B137" s="17" t="inlineStr">
+      <c r="B137" s="16" t="inlineStr">
         <is>
           <t>template_id</t>
         </is>
       </c>
-      <c r="C137" s="17" t="inlineStr">
+      <c r="C137" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D137" s="24" t="inlineStr">
+      <c r="D137" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E137" s="19" t="inlineStr">
+      <c r="E137" s="18" t="inlineStr">
         <is>
           <t>module_template(id)</t>
         </is>
       </c>
-      <c r="F137" s="23" t="inlineStr">
+      <c r="F137" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -4968,19 +4927,19 @@
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr"/>
-      <c r="B138" s="17" t="inlineStr">
+      <c r="B138" s="16" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C138" s="21" t="inlineStr">
+      <c r="C138" s="20" t="inlineStr">
         <is>
           <t>varchar(120)</t>
         </is>
       </c>
-      <c r="D138" s="22" t="inlineStr"/>
-      <c r="E138" s="19" t="inlineStr"/>
-      <c r="F138" s="20" t="inlineStr">
+      <c r="D138" s="21" t="inlineStr"/>
+      <c r="E138" s="18" t="inlineStr"/>
+      <c r="F138" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -4989,19 +4948,19 @@
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr"/>
-      <c r="B139" s="17" t="inlineStr">
+      <c r="B139" s="16" t="inlineStr">
         <is>
           <t>module_kind</t>
         </is>
       </c>
-      <c r="C139" s="21" t="inlineStr">
+      <c r="C139" s="20" t="inlineStr">
         <is>
           <t>varchar(40)</t>
         </is>
       </c>
-      <c r="D139" s="22" t="inlineStr"/>
-      <c r="E139" s="19" t="inlineStr"/>
-      <c r="F139" s="23" t="inlineStr">
+      <c r="D139" s="21" t="inlineStr"/>
+      <c r="E139" s="18" t="inlineStr"/>
+      <c r="F139" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5014,19 +4973,19 @@
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr"/>
-      <c r="B140" s="17" t="inlineStr">
+      <c r="B140" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C140" s="21" t="inlineStr">
+      <c r="C140" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D140" s="22" t="inlineStr"/>
-      <c r="E140" s="19" t="inlineStr"/>
-      <c r="F140" s="20" t="inlineStr">
+      <c r="D140" s="21" t="inlineStr"/>
+      <c r="E140" s="18" t="inlineStr"/>
+      <c r="F140" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5034,37 +4993,37 @@
       <c r="G140" s="4" t="inlineStr"/>
     </row>
     <row r="141" ht="4" customHeight="1">
-      <c r="A141" s="25" t="n"/>
-      <c r="B141" s="25" t="n"/>
-      <c r="C141" s="25" t="n"/>
-      <c r="D141" s="25" t="n"/>
-      <c r="E141" s="25" t="n"/>
-      <c r="F141" s="25" t="n"/>
-      <c r="G141" s="25" t="n"/>
+      <c r="A141" s="24" t="n"/>
+      <c r="B141" s="24" t="n"/>
+      <c r="C141" s="24" t="n"/>
+      <c r="D141" s="24" t="n"/>
+      <c r="E141" s="24" t="n"/>
+      <c r="F141" s="24" t="n"/>
+      <c r="G141" s="24" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="15" t="inlineStr">
+      <c r="A142" s="14" t="inlineStr">
         <is>
           <t>module_lecture</t>
         </is>
       </c>
-      <c r="B142" s="16" t="inlineStr">
+      <c r="B142" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C142" s="17" t="inlineStr">
+      <c r="C142" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D142" s="18" t="inlineStr">
+      <c r="D142" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E142" s="19" t="inlineStr"/>
-      <c r="F142" s="20" t="inlineStr">
+      <c r="E142" s="18" t="inlineStr"/>
+      <c r="F142" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5073,27 +5032,27 @@
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr"/>
-      <c r="B143" s="17" t="inlineStr">
+      <c r="B143" s="16" t="inlineStr">
         <is>
           <t>module_id</t>
         </is>
       </c>
-      <c r="C143" s="17" t="inlineStr">
+      <c r="C143" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D143" s="24" t="inlineStr">
+      <c r="D143" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E143" s="19" t="inlineStr">
+      <c r="E143" s="18" t="inlineStr">
         <is>
           <t>module(id)</t>
         </is>
       </c>
-      <c r="F143" s="20" t="inlineStr">
+      <c r="F143" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5102,27 +5061,27 @@
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr"/>
-      <c r="B144" s="17" t="inlineStr">
+      <c r="B144" s="16" t="inlineStr">
         <is>
           <t>template_lecture_id</t>
         </is>
       </c>
-      <c r="C144" s="17" t="inlineStr">
+      <c r="C144" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D144" s="24" t="inlineStr">
+      <c r="D144" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E144" s="19" t="inlineStr">
+      <c r="E144" s="18" t="inlineStr">
         <is>
           <t>template_lecture(id)</t>
         </is>
       </c>
-      <c r="F144" s="23" t="inlineStr">
+      <c r="F144" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5135,19 +5094,19 @@
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr"/>
-      <c r="B145" s="17" t="inlineStr">
+      <c r="B145" s="16" t="inlineStr">
         <is>
           <t>semester_no</t>
         </is>
       </c>
-      <c r="C145" s="17" t="inlineStr">
+      <c r="C145" s="16" t="inlineStr">
         <is>
           <t>smallint</t>
         </is>
       </c>
-      <c r="D145" s="22" t="inlineStr"/>
-      <c r="E145" s="19" t="inlineStr"/>
-      <c r="F145" s="20" t="inlineStr">
+      <c r="D145" s="21" t="inlineStr"/>
+      <c r="E145" s="18" t="inlineStr"/>
+      <c r="F145" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5156,19 +5115,19 @@
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr"/>
-      <c r="B146" s="17" t="inlineStr">
+      <c r="B146" s="16" t="inlineStr">
         <is>
           <t>sequence_no</t>
         </is>
       </c>
-      <c r="C146" s="17" t="inlineStr">
+      <c r="C146" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D146" s="22" t="inlineStr"/>
-      <c r="E146" s="19" t="inlineStr"/>
-      <c r="F146" s="20" t="inlineStr">
+      <c r="D146" s="21" t="inlineStr"/>
+      <c r="E146" s="18" t="inlineStr"/>
+      <c r="F146" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5177,19 +5136,19 @@
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr"/>
-      <c r="B147" s="17" t="inlineStr">
+      <c r="B147" s="16" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C147" s="21" t="inlineStr">
+      <c r="C147" s="20" t="inlineStr">
         <is>
           <t>varchar(160)</t>
         </is>
       </c>
-      <c r="D147" s="22" t="inlineStr"/>
-      <c r="E147" s="19" t="inlineStr"/>
-      <c r="F147" s="20" t="inlineStr">
+      <c r="D147" s="21" t="inlineStr"/>
+      <c r="E147" s="18" t="inlineStr"/>
+      <c r="F147" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5198,19 +5157,19 @@
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr"/>
-      <c r="B148" s="17" t="inlineStr">
+      <c r="B148" s="16" t="inlineStr">
         <is>
           <t>lecture_type</t>
         </is>
       </c>
-      <c r="C148" s="21" t="inlineStr">
+      <c r="C148" s="20" t="inlineStr">
         <is>
           <t>lecture_type</t>
         </is>
       </c>
-      <c r="D148" s="22" t="inlineStr"/>
-      <c r="E148" s="19" t="inlineStr"/>
-      <c r="F148" s="20" t="inlineStr">
+      <c r="D148" s="21" t="inlineStr"/>
+      <c r="E148" s="18" t="inlineStr"/>
+      <c r="F148" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5223,19 +5182,19 @@
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr"/>
-      <c r="B149" s="17" t="inlineStr">
+      <c r="B149" s="16" t="inlineStr">
         <is>
           <t>duration_min</t>
         </is>
       </c>
-      <c r="C149" s="17" t="inlineStr">
+      <c r="C149" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D149" s="22" t="inlineStr"/>
-      <c r="E149" s="19" t="inlineStr"/>
-      <c r="F149" s="23" t="inlineStr">
+      <c r="D149" s="21" t="inlineStr"/>
+      <c r="E149" s="18" t="inlineStr"/>
+      <c r="F149" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5244,19 +5203,19 @@
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr"/>
-      <c r="B150" s="17" t="inlineStr">
+      <c r="B150" s="16" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C150" s="17" t="inlineStr">
+      <c r="C150" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D150" s="22" t="inlineStr"/>
-      <c r="E150" s="19" t="inlineStr"/>
-      <c r="F150" s="23" t="inlineStr">
+      <c r="D150" s="21" t="inlineStr"/>
+      <c r="E150" s="18" t="inlineStr"/>
+      <c r="F150" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5265,19 +5224,19 @@
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr"/>
-      <c r="B151" s="17" t="inlineStr">
+      <c r="B151" s="16" t="inlineStr">
         <is>
           <t>is_conducted</t>
         </is>
       </c>
-      <c r="C151" s="17" t="inlineStr">
+      <c r="C151" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="D151" s="22" t="inlineStr"/>
-      <c r="E151" s="19" t="inlineStr"/>
-      <c r="F151" s="20" t="inlineStr">
+      <c r="D151" s="21" t="inlineStr"/>
+      <c r="E151" s="18" t="inlineStr"/>
+      <c r="F151" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5290,19 +5249,19 @@
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr"/>
-      <c r="B152" s="17" t="inlineStr">
+      <c r="B152" s="16" t="inlineStr">
         <is>
           <t>conducted_on</t>
         </is>
       </c>
-      <c r="C152" s="17" t="inlineStr">
+      <c r="C152" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D152" s="22" t="inlineStr"/>
-      <c r="E152" s="19" t="inlineStr"/>
-      <c r="F152" s="23" t="inlineStr">
+      <c r="D152" s="21" t="inlineStr"/>
+      <c r="E152" s="18" t="inlineStr"/>
+      <c r="F152" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5310,37 +5269,37 @@
       <c r="G152" s="4" t="inlineStr"/>
     </row>
     <row r="153" ht="4" customHeight="1">
-      <c r="A153" s="25" t="n"/>
-      <c r="B153" s="25" t="n"/>
-      <c r="C153" s="25" t="n"/>
-      <c r="D153" s="25" t="n"/>
-      <c r="E153" s="25" t="n"/>
-      <c r="F153" s="25" t="n"/>
-      <c r="G153" s="25" t="n"/>
+      <c r="A153" s="24" t="n"/>
+      <c r="B153" s="24" t="n"/>
+      <c r="C153" s="24" t="n"/>
+      <c r="D153" s="24" t="n"/>
+      <c r="E153" s="24" t="n"/>
+      <c r="F153" s="24" t="n"/>
+      <c r="G153" s="24" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="15" t="inlineStr">
+      <c r="A154" s="14" t="inlineStr">
         <is>
           <t>lecture_material</t>
         </is>
       </c>
-      <c r="B154" s="16" t="inlineStr">
+      <c r="B154" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C154" s="17" t="inlineStr">
+      <c r="C154" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D154" s="18" t="inlineStr">
+      <c r="D154" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E154" s="19" t="inlineStr"/>
-      <c r="F154" s="20" t="inlineStr">
+      <c r="E154" s="18" t="inlineStr"/>
+      <c r="F154" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5349,27 +5308,27 @@
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr"/>
-      <c r="B155" s="17" t="inlineStr">
+      <c r="B155" s="16" t="inlineStr">
         <is>
           <t>module_lecture_id</t>
         </is>
       </c>
-      <c r="C155" s="17" t="inlineStr">
+      <c r="C155" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D155" s="24" t="inlineStr">
+      <c r="D155" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E155" s="19" t="inlineStr">
+      <c r="E155" s="18" t="inlineStr">
         <is>
           <t>module_lecture(id)</t>
         </is>
       </c>
-      <c r="F155" s="23" t="inlineStr">
+      <c r="F155" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5382,27 +5341,27 @@
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr"/>
-      <c r="B156" s="17" t="inlineStr">
+      <c r="B156" s="16" t="inlineStr">
         <is>
           <t>template_lecture_id</t>
         </is>
       </c>
-      <c r="C156" s="17" t="inlineStr">
+      <c r="C156" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D156" s="24" t="inlineStr">
+      <c r="D156" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E156" s="19" t="inlineStr">
+      <c r="E156" s="18" t="inlineStr">
         <is>
           <t>template_lecture(id)</t>
         </is>
       </c>
-      <c r="F156" s="23" t="inlineStr">
+      <c r="F156" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5415,19 +5374,19 @@
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr"/>
-      <c r="B157" s="17" t="inlineStr">
+      <c r="B157" s="16" t="inlineStr">
         <is>
           <t>material_type</t>
         </is>
       </c>
-      <c r="C157" s="21" t="inlineStr">
+      <c r="C157" s="20" t="inlineStr">
         <is>
           <t>material_type</t>
         </is>
       </c>
-      <c r="D157" s="22" t="inlineStr"/>
-      <c r="E157" s="19" t="inlineStr"/>
-      <c r="F157" s="20" t="inlineStr">
+      <c r="D157" s="21" t="inlineStr"/>
+      <c r="E157" s="18" t="inlineStr"/>
+      <c r="F157" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5440,19 +5399,19 @@
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr"/>
-      <c r="B158" s="17" t="inlineStr">
+      <c r="B158" s="16" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C158" s="21" t="inlineStr">
+      <c r="C158" s="20" t="inlineStr">
         <is>
           <t>varchar(160)</t>
         </is>
       </c>
-      <c r="D158" s="22" t="inlineStr"/>
-      <c r="E158" s="19" t="inlineStr"/>
-      <c r="F158" s="23" t="inlineStr">
+      <c r="D158" s="21" t="inlineStr"/>
+      <c r="E158" s="18" t="inlineStr"/>
+      <c r="F158" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5461,19 +5420,19 @@
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr"/>
-      <c r="B159" s="17" t="inlineStr">
+      <c r="B159" s="16" t="inlineStr">
         <is>
           <t>file_url</t>
         </is>
       </c>
-      <c r="C159" s="21" t="inlineStr">
+      <c r="C159" s="20" t="inlineStr">
         <is>
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="D159" s="22" t="inlineStr"/>
-      <c r="E159" s="19" t="inlineStr"/>
-      <c r="F159" s="23" t="inlineStr">
+      <c r="D159" s="21" t="inlineStr"/>
+      <c r="E159" s="18" t="inlineStr"/>
+      <c r="F159" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5482,19 +5441,19 @@
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr"/>
-      <c r="B160" s="17" t="inlineStr">
+      <c r="B160" s="16" t="inlineStr">
         <is>
           <t>external_link</t>
         </is>
       </c>
-      <c r="C160" s="21" t="inlineStr">
+      <c r="C160" s="20" t="inlineStr">
         <is>
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="D160" s="22" t="inlineStr"/>
-      <c r="E160" s="19" t="inlineStr"/>
-      <c r="F160" s="23" t="inlineStr">
+      <c r="D160" s="21" t="inlineStr"/>
+      <c r="E160" s="18" t="inlineStr"/>
+      <c r="F160" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5503,19 +5462,19 @@
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr"/>
-      <c r="B161" s="17" t="inlineStr">
+      <c r="B161" s="16" t="inlineStr">
         <is>
           <t>is_downloadable</t>
         </is>
       </c>
-      <c r="C161" s="17" t="inlineStr">
+      <c r="C161" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="D161" s="22" t="inlineStr"/>
-      <c r="E161" s="19" t="inlineStr"/>
-      <c r="F161" s="20" t="inlineStr">
+      <c r="D161" s="21" t="inlineStr"/>
+      <c r="E161" s="18" t="inlineStr"/>
+      <c r="F161" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5528,19 +5487,19 @@
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr"/>
-      <c r="B162" s="17" t="inlineStr">
+      <c r="B162" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C162" s="21" t="inlineStr">
+      <c r="C162" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D162" s="22" t="inlineStr"/>
-      <c r="E162" s="19" t="inlineStr"/>
-      <c r="F162" s="20" t="inlineStr">
+      <c r="D162" s="21" t="inlineStr"/>
+      <c r="E162" s="18" t="inlineStr"/>
+      <c r="F162" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5548,37 +5507,37 @@
       <c r="G162" s="4" t="inlineStr"/>
     </row>
     <row r="163" ht="4" customHeight="1">
-      <c r="A163" s="25" t="n"/>
-      <c r="B163" s="25" t="n"/>
-      <c r="C163" s="25" t="n"/>
-      <c r="D163" s="25" t="n"/>
-      <c r="E163" s="25" t="n"/>
-      <c r="F163" s="25" t="n"/>
-      <c r="G163" s="25" t="n"/>
+      <c r="A163" s="24" t="n"/>
+      <c r="B163" s="24" t="n"/>
+      <c r="C163" s="24" t="n"/>
+      <c r="D163" s="24" t="n"/>
+      <c r="E163" s="24" t="n"/>
+      <c r="F163" s="24" t="n"/>
+      <c r="G163" s="24" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="15" t="inlineStr">
+      <c r="A164" s="14" t="inlineStr">
         <is>
           <t>lesson</t>
         </is>
       </c>
-      <c r="B164" s="16" t="inlineStr">
+      <c r="B164" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C164" s="17" t="inlineStr">
+      <c r="C164" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D164" s="18" t="inlineStr">
+      <c r="D164" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E164" s="19" t="inlineStr"/>
-      <c r="F164" s="20" t="inlineStr">
+      <c r="E164" s="18" t="inlineStr"/>
+      <c r="F164" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5587,27 +5546,27 @@
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr"/>
-      <c r="B165" s="17" t="inlineStr">
+      <c r="B165" s="16" t="inlineStr">
         <is>
           <t>group_id</t>
         </is>
       </c>
-      <c r="C165" s="17" t="inlineStr">
+      <c r="C165" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D165" s="24" t="inlineStr">
+      <c r="D165" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E165" s="19" t="inlineStr">
+      <c r="E165" s="18" t="inlineStr">
         <is>
           <t>study_group(id)</t>
         </is>
       </c>
-      <c r="F165" s="20" t="inlineStr">
+      <c r="F165" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5616,27 +5575,27 @@
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr"/>
-      <c r="B166" s="17" t="inlineStr">
+      <c r="B166" s="16" t="inlineStr">
         <is>
           <t>module_lecture_id</t>
         </is>
       </c>
-      <c r="C166" s="17" t="inlineStr">
+      <c r="C166" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D166" s="24" t="inlineStr">
+      <c r="D166" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E166" s="19" t="inlineStr">
+      <c r="E166" s="18" t="inlineStr">
         <is>
           <t>module_lecture(id)</t>
         </is>
       </c>
-      <c r="F166" s="20" t="inlineStr">
+      <c r="F166" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5645,27 +5604,27 @@
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr"/>
-      <c r="B167" s="17" t="inlineStr">
+      <c r="B167" s="16" t="inlineStr">
         <is>
           <t>trainer_id</t>
         </is>
       </c>
-      <c r="C167" s="17" t="inlineStr">
+      <c r="C167" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D167" s="24" t="inlineStr">
+      <c r="D167" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E167" s="19" t="inlineStr">
+      <c r="E167" s="18" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
       </c>
-      <c r="F167" s="23" t="inlineStr">
+      <c r="F167" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5678,19 +5637,19 @@
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr"/>
-      <c r="B168" s="17" t="inlineStr">
+      <c r="B168" s="16" t="inlineStr">
         <is>
           <t>scheduled_date</t>
         </is>
       </c>
-      <c r="C168" s="17" t="inlineStr">
+      <c r="C168" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D168" s="22" t="inlineStr"/>
-      <c r="E168" s="19" t="inlineStr"/>
-      <c r="F168" s="20" t="inlineStr">
+      <c r="D168" s="21" t="inlineStr"/>
+      <c r="E168" s="18" t="inlineStr"/>
+      <c r="F168" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5699,19 +5658,19 @@
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr"/>
-      <c r="B169" s="17" t="inlineStr">
+      <c r="B169" s="16" t="inlineStr">
         <is>
           <t>start_time</t>
         </is>
       </c>
-      <c r="C169" s="21" t="inlineStr">
+      <c r="C169" s="20" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="D169" s="22" t="inlineStr"/>
-      <c r="E169" s="19" t="inlineStr"/>
-      <c r="F169" s="23" t="inlineStr">
+      <c r="D169" s="21" t="inlineStr"/>
+      <c r="E169" s="18" t="inlineStr"/>
+      <c r="F169" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5720,19 +5679,19 @@
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr"/>
-      <c r="B170" s="17" t="inlineStr">
+      <c r="B170" s="16" t="inlineStr">
         <is>
           <t>end_time</t>
         </is>
       </c>
-      <c r="C170" s="21" t="inlineStr">
+      <c r="C170" s="20" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="D170" s="22" t="inlineStr"/>
-      <c r="E170" s="19" t="inlineStr"/>
-      <c r="F170" s="23" t="inlineStr">
+      <c r="D170" s="21" t="inlineStr"/>
+      <c r="E170" s="18" t="inlineStr"/>
+      <c r="F170" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5741,19 +5700,19 @@
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr"/>
-      <c r="B171" s="17" t="inlineStr">
+      <c r="B171" s="16" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C171" s="21" t="inlineStr">
+      <c r="C171" s="20" t="inlineStr">
         <is>
           <t>lesson_status</t>
         </is>
       </c>
-      <c r="D171" s="22" t="inlineStr"/>
-      <c r="E171" s="19" t="inlineStr"/>
-      <c r="F171" s="20" t="inlineStr">
+      <c r="D171" s="21" t="inlineStr"/>
+      <c r="E171" s="18" t="inlineStr"/>
+      <c r="F171" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5766,19 +5725,19 @@
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr"/>
-      <c r="B172" s="17" t="inlineStr">
+      <c r="B172" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C172" s="21" t="inlineStr">
+      <c r="C172" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D172" s="22" t="inlineStr"/>
-      <c r="E172" s="19" t="inlineStr"/>
-      <c r="F172" s="20" t="inlineStr">
+      <c r="D172" s="21" t="inlineStr"/>
+      <c r="E172" s="18" t="inlineStr"/>
+      <c r="F172" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5786,37 +5745,37 @@
       <c r="G172" s="4" t="inlineStr"/>
     </row>
     <row r="173" ht="4" customHeight="1">
-      <c r="A173" s="25" t="n"/>
-      <c r="B173" s="25" t="n"/>
-      <c r="C173" s="25" t="n"/>
-      <c r="D173" s="25" t="n"/>
-      <c r="E173" s="25" t="n"/>
-      <c r="F173" s="25" t="n"/>
-      <c r="G173" s="25" t="n"/>
+      <c r="A173" s="24" t="n"/>
+      <c r="B173" s="24" t="n"/>
+      <c r="C173" s="24" t="n"/>
+      <c r="D173" s="24" t="n"/>
+      <c r="E173" s="24" t="n"/>
+      <c r="F173" s="24" t="n"/>
+      <c r="G173" s="24" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="15" t="inlineStr">
+      <c r="A174" s="14" t="inlineStr">
         <is>
           <t>attendance</t>
         </is>
       </c>
-      <c r="B174" s="16" t="inlineStr">
+      <c r="B174" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C174" s="17" t="inlineStr">
+      <c r="C174" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D174" s="18" t="inlineStr">
+      <c r="D174" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E174" s="19" t="inlineStr"/>
-      <c r="F174" s="20" t="inlineStr">
+      <c r="E174" s="18" t="inlineStr"/>
+      <c r="F174" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5825,27 +5784,27 @@
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr"/>
-      <c r="B175" s="17" t="inlineStr">
+      <c r="B175" s="16" t="inlineStr">
         <is>
           <t>lesson_id</t>
         </is>
       </c>
-      <c r="C175" s="17" t="inlineStr">
+      <c r="C175" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D175" s="24" t="inlineStr">
+      <c r="D175" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E175" s="19" t="inlineStr">
+      <c r="E175" s="18" t="inlineStr">
         <is>
           <t>lesson(id)</t>
         </is>
       </c>
-      <c r="F175" s="20" t="inlineStr">
+      <c r="F175" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5854,27 +5813,27 @@
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr"/>
-      <c r="B176" s="17" t="inlineStr">
+      <c r="B176" s="16" t="inlineStr">
         <is>
           <t>student_id</t>
         </is>
       </c>
-      <c r="C176" s="17" t="inlineStr">
+      <c r="C176" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D176" s="24" t="inlineStr">
+      <c r="D176" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E176" s="19" t="inlineStr">
+      <c r="E176" s="18" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
       </c>
-      <c r="F176" s="20" t="inlineStr">
+      <c r="F176" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5883,19 +5842,19 @@
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr"/>
-      <c r="B177" s="17" t="inlineStr">
+      <c r="B177" s="16" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C177" s="21" t="inlineStr">
+      <c r="C177" s="20" t="inlineStr">
         <is>
           <t>attendance_status</t>
         </is>
       </c>
-      <c r="D177" s="22" t="inlineStr"/>
-      <c r="E177" s="19" t="inlineStr"/>
-      <c r="F177" s="20" t="inlineStr">
+      <c r="D177" s="21" t="inlineStr"/>
+      <c r="E177" s="18" t="inlineStr"/>
+      <c r="F177" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -5908,27 +5867,27 @@
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr"/>
-      <c r="B178" s="17" t="inlineStr">
+      <c r="B178" s="16" t="inlineStr">
         <is>
           <t>recorded_by</t>
         </is>
       </c>
-      <c r="C178" s="17" t="inlineStr">
+      <c r="C178" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D178" s="24" t="inlineStr">
+      <c r="D178" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E178" s="19" t="inlineStr">
+      <c r="E178" s="18" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
       </c>
-      <c r="F178" s="23" t="inlineStr">
+      <c r="F178" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5937,19 +5896,19 @@
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr"/>
-      <c r="B179" s="17" t="inlineStr">
+      <c r="B179" s="16" t="inlineStr">
         <is>
           <t>recorded_at</t>
         </is>
       </c>
-      <c r="C179" s="21" t="inlineStr">
+      <c r="C179" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D179" s="22" t="inlineStr"/>
-      <c r="E179" s="19" t="inlineStr"/>
-      <c r="F179" s="23" t="inlineStr">
+      <c r="D179" s="21" t="inlineStr"/>
+      <c r="E179" s="18" t="inlineStr"/>
+      <c r="F179" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -5958,23 +5917,23 @@
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr"/>
-      <c r="B180" s="17" t="inlineStr">
+      <c r="B180" s="16" t="inlineStr">
         <is>
           <t>uq_att</t>
         </is>
       </c>
-      <c r="C180" s="17" t="inlineStr">
+      <c r="C180" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D180" s="26" t="inlineStr">
+      <c r="D180" s="25" t="inlineStr">
         <is>
           <t>UQ</t>
         </is>
       </c>
-      <c r="E180" s="19" t="inlineStr"/>
-      <c r="F180" s="23" t="inlineStr"/>
+      <c r="E180" s="18" t="inlineStr"/>
+      <c r="F180" s="22" t="inlineStr"/>
       <c r="G180" s="4" t="inlineStr">
         <is>
           <t>UNIQUE(lesson_id, student_id)</t>
@@ -5982,37 +5941,37 @@
       </c>
     </row>
     <row r="181" ht="4" customHeight="1">
-      <c r="A181" s="25" t="n"/>
-      <c r="B181" s="25" t="n"/>
-      <c r="C181" s="25" t="n"/>
-      <c r="D181" s="25" t="n"/>
-      <c r="E181" s="25" t="n"/>
-      <c r="F181" s="25" t="n"/>
-      <c r="G181" s="25" t="n"/>
+      <c r="A181" s="24" t="n"/>
+      <c r="B181" s="24" t="n"/>
+      <c r="C181" s="24" t="n"/>
+      <c r="D181" s="24" t="n"/>
+      <c r="E181" s="24" t="n"/>
+      <c r="F181" s="24" t="n"/>
+      <c r="G181" s="24" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="15" t="inlineStr">
+      <c r="A182" s="14" t="inlineStr">
         <is>
           <t>exam</t>
         </is>
       </c>
-      <c r="B182" s="16" t="inlineStr">
+      <c r="B182" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C182" s="17" t="inlineStr">
+      <c r="C182" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D182" s="18" t="inlineStr">
+      <c r="D182" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E182" s="19" t="inlineStr"/>
-      <c r="F182" s="20" t="inlineStr">
+      <c r="E182" s="18" t="inlineStr"/>
+      <c r="F182" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6021,27 +5980,27 @@
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr"/>
-      <c r="B183" s="17" t="inlineStr">
+      <c r="B183" s="16" t="inlineStr">
         <is>
           <t>group_id</t>
         </is>
       </c>
-      <c r="C183" s="17" t="inlineStr">
+      <c r="C183" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D183" s="24" t="inlineStr">
+      <c r="D183" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E183" s="19" t="inlineStr">
+      <c r="E183" s="18" t="inlineStr">
         <is>
           <t>study_group(id)</t>
         </is>
       </c>
-      <c r="F183" s="20" t="inlineStr">
+      <c r="F183" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6050,27 +6009,27 @@
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr"/>
-      <c r="B184" s="17" t="inlineStr">
+      <c r="B184" s="16" t="inlineStr">
         <is>
           <t>module_lecture_id</t>
         </is>
       </c>
-      <c r="C184" s="17" t="inlineStr">
+      <c r="C184" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D184" s="24" t="inlineStr">
+      <c r="D184" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E184" s="19" t="inlineStr">
+      <c r="E184" s="18" t="inlineStr">
         <is>
           <t>module_lecture(id)</t>
         </is>
       </c>
-      <c r="F184" s="23" t="inlineStr">
+      <c r="F184" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6079,19 +6038,19 @@
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr"/>
-      <c r="B185" s="17" t="inlineStr">
+      <c r="B185" s="16" t="inlineStr">
         <is>
           <t>exam_type</t>
         </is>
       </c>
-      <c r="C185" s="21" t="inlineStr">
+      <c r="C185" s="20" t="inlineStr">
         <is>
           <t>exam_type</t>
         </is>
       </c>
-      <c r="D185" s="22" t="inlineStr"/>
-      <c r="E185" s="19" t="inlineStr"/>
-      <c r="F185" s="20" t="inlineStr">
+      <c r="D185" s="21" t="inlineStr"/>
+      <c r="E185" s="18" t="inlineStr"/>
+      <c r="F185" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6104,19 +6063,19 @@
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr"/>
-      <c r="B186" s="17" t="inlineStr">
+      <c r="B186" s="16" t="inlineStr">
         <is>
           <t>exam_date</t>
         </is>
       </c>
-      <c r="C186" s="17" t="inlineStr">
+      <c r="C186" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D186" s="22" t="inlineStr"/>
-      <c r="E186" s="19" t="inlineStr"/>
-      <c r="F186" s="23" t="inlineStr">
+      <c r="D186" s="21" t="inlineStr"/>
+      <c r="E186" s="18" t="inlineStr"/>
+      <c r="F186" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6125,19 +6084,19 @@
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr"/>
-      <c r="B187" s="17" t="inlineStr">
+      <c r="B187" s="16" t="inlineStr">
         <is>
           <t>max_score</t>
         </is>
       </c>
-      <c r="C187" s="21" t="inlineStr">
+      <c r="C187" s="20" t="inlineStr">
         <is>
           <t>numeric(5,2)</t>
         </is>
       </c>
-      <c r="D187" s="22" t="inlineStr"/>
-      <c r="E187" s="19" t="inlineStr"/>
-      <c r="F187" s="23" t="inlineStr">
+      <c r="D187" s="21" t="inlineStr"/>
+      <c r="E187" s="18" t="inlineStr"/>
+      <c r="F187" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6146,19 +6105,19 @@
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr"/>
-      <c r="B188" s="17" t="inlineStr">
+      <c r="B188" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C188" s="21" t="inlineStr">
+      <c r="C188" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D188" s="22" t="inlineStr"/>
-      <c r="E188" s="19" t="inlineStr"/>
-      <c r="F188" s="20" t="inlineStr">
+      <c r="D188" s="21" t="inlineStr"/>
+      <c r="E188" s="18" t="inlineStr"/>
+      <c r="F188" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6166,37 +6125,37 @@
       <c r="G188" s="4" t="inlineStr"/>
     </row>
     <row r="189" ht="4" customHeight="1">
-      <c r="A189" s="25" t="n"/>
-      <c r="B189" s="25" t="n"/>
-      <c r="C189" s="25" t="n"/>
-      <c r="D189" s="25" t="n"/>
-      <c r="E189" s="25" t="n"/>
-      <c r="F189" s="25" t="n"/>
-      <c r="G189" s="25" t="n"/>
+      <c r="A189" s="24" t="n"/>
+      <c r="B189" s="24" t="n"/>
+      <c r="C189" s="24" t="n"/>
+      <c r="D189" s="24" t="n"/>
+      <c r="E189" s="24" t="n"/>
+      <c r="F189" s="24" t="n"/>
+      <c r="G189" s="24" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="15" t="inlineStr">
+      <c r="A190" s="14" t="inlineStr">
         <is>
           <t>exam_result</t>
         </is>
       </c>
-      <c r="B190" s="16" t="inlineStr">
+      <c r="B190" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C190" s="17" t="inlineStr">
+      <c r="C190" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D190" s="18" t="inlineStr">
+      <c r="D190" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E190" s="19" t="inlineStr"/>
-      <c r="F190" s="20" t="inlineStr">
+      <c r="E190" s="18" t="inlineStr"/>
+      <c r="F190" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6205,27 +6164,27 @@
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr"/>
-      <c r="B191" s="17" t="inlineStr">
+      <c r="B191" s="16" t="inlineStr">
         <is>
           <t>exam_id</t>
         </is>
       </c>
-      <c r="C191" s="17" t="inlineStr">
+      <c r="C191" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D191" s="24" t="inlineStr">
+      <c r="D191" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E191" s="19" t="inlineStr">
+      <c r="E191" s="18" t="inlineStr">
         <is>
           <t>exam(id)</t>
         </is>
       </c>
-      <c r="F191" s="20" t="inlineStr">
+      <c r="F191" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6234,27 +6193,27 @@
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr"/>
-      <c r="B192" s="17" t="inlineStr">
+      <c r="B192" s="16" t="inlineStr">
         <is>
           <t>student_id</t>
         </is>
       </c>
-      <c r="C192" s="17" t="inlineStr">
+      <c r="C192" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D192" s="24" t="inlineStr">
+      <c r="D192" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E192" s="19" t="inlineStr">
+      <c r="E192" s="18" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
       </c>
-      <c r="F192" s="20" t="inlineStr">
+      <c r="F192" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6263,19 +6222,19 @@
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr"/>
-      <c r="B193" s="17" t="inlineStr">
+      <c r="B193" s="16" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="C193" s="21" t="inlineStr">
+      <c r="C193" s="20" t="inlineStr">
         <is>
           <t>numeric(5,2)</t>
         </is>
       </c>
-      <c r="D193" s="22" t="inlineStr"/>
-      <c r="E193" s="19" t="inlineStr"/>
-      <c r="F193" s="23" t="inlineStr">
+      <c r="D193" s="21" t="inlineStr"/>
+      <c r="E193" s="18" t="inlineStr"/>
+      <c r="F193" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6284,19 +6243,19 @@
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr"/>
-      <c r="B194" s="17" t="inlineStr">
+      <c r="B194" s="16" t="inlineStr">
         <is>
           <t>attended</t>
         </is>
       </c>
-      <c r="C194" s="17" t="inlineStr">
+      <c r="C194" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="D194" s="22" t="inlineStr"/>
-      <c r="E194" s="19" t="inlineStr"/>
-      <c r="F194" s="20" t="inlineStr">
+      <c r="D194" s="21" t="inlineStr"/>
+      <c r="E194" s="18" t="inlineStr"/>
+      <c r="F194" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6305,19 +6264,19 @@
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr"/>
-      <c r="B195" s="17" t="inlineStr">
+      <c r="B195" s="16" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="C195" s="21" t="inlineStr">
+      <c r="C195" s="20" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="D195" s="22" t="inlineStr"/>
-      <c r="E195" s="19" t="inlineStr"/>
-      <c r="F195" s="23" t="inlineStr">
+      <c r="D195" s="21" t="inlineStr"/>
+      <c r="E195" s="18" t="inlineStr"/>
+      <c r="F195" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6326,27 +6285,27 @@
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr"/>
-      <c r="B196" s="17" t="inlineStr">
+      <c r="B196" s="16" t="inlineStr">
         <is>
           <t>recorded_by</t>
         </is>
       </c>
-      <c r="C196" s="17" t="inlineStr">
+      <c r="C196" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D196" s="24" t="inlineStr">
+      <c r="D196" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E196" s="19" t="inlineStr">
+      <c r="E196" s="18" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
       </c>
-      <c r="F196" s="23" t="inlineStr">
+      <c r="F196" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6355,23 +6314,23 @@
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr"/>
-      <c r="B197" s="17" t="inlineStr">
+      <c r="B197" s="16" t="inlineStr">
         <is>
           <t>uq_res</t>
         </is>
       </c>
-      <c r="C197" s="17" t="inlineStr">
+      <c r="C197" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D197" s="26" t="inlineStr">
+      <c r="D197" s="25" t="inlineStr">
         <is>
           <t>UQ</t>
         </is>
       </c>
-      <c r="E197" s="19" t="inlineStr"/>
-      <c r="F197" s="23" t="inlineStr"/>
+      <c r="E197" s="18" t="inlineStr"/>
+      <c r="F197" s="22" t="inlineStr"/>
       <c r="G197" s="4" t="inlineStr">
         <is>
           <t>UNIQUE(exam_id, student_id)</t>
@@ -6379,37 +6338,37 @@
       </c>
     </row>
     <row r="198" ht="4" customHeight="1">
-      <c r="A198" s="25" t="n"/>
-      <c r="B198" s="25" t="n"/>
-      <c r="C198" s="25" t="n"/>
-      <c r="D198" s="25" t="n"/>
-      <c r="E198" s="25" t="n"/>
-      <c r="F198" s="25" t="n"/>
-      <c r="G198" s="25" t="n"/>
+      <c r="A198" s="24" t="n"/>
+      <c r="B198" s="24" t="n"/>
+      <c r="C198" s="24" t="n"/>
+      <c r="D198" s="24" t="n"/>
+      <c r="E198" s="24" t="n"/>
+      <c r="F198" s="24" t="n"/>
+      <c r="G198" s="24" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="15" t="inlineStr">
+      <c r="A199" s="14" t="inlineStr">
         <is>
           <t>homework</t>
         </is>
       </c>
-      <c r="B199" s="16" t="inlineStr">
+      <c r="B199" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C199" s="17" t="inlineStr">
+      <c r="C199" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D199" s="18" t="inlineStr">
+      <c r="D199" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E199" s="19" t="inlineStr"/>
-      <c r="F199" s="20" t="inlineStr">
+      <c r="E199" s="18" t="inlineStr"/>
+      <c r="F199" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6418,27 +6377,27 @@
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr"/>
-      <c r="B200" s="17" t="inlineStr">
+      <c r="B200" s="16" t="inlineStr">
         <is>
           <t>module_lecture_id</t>
         </is>
       </c>
-      <c r="C200" s="17" t="inlineStr">
+      <c r="C200" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D200" s="24" t="inlineStr">
+      <c r="D200" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E200" s="19" t="inlineStr">
+      <c r="E200" s="18" t="inlineStr">
         <is>
           <t>module_lecture(id)</t>
         </is>
       </c>
-      <c r="F200" s="23" t="inlineStr">
+      <c r="F200" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6447,27 +6406,27 @@
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr"/>
-      <c r="B201" s="17" t="inlineStr">
+      <c r="B201" s="16" t="inlineStr">
         <is>
           <t>lesson_id</t>
         </is>
       </c>
-      <c r="C201" s="17" t="inlineStr">
+      <c r="C201" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D201" s="24" t="inlineStr">
+      <c r="D201" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E201" s="19" t="inlineStr">
+      <c r="E201" s="18" t="inlineStr">
         <is>
           <t>lesson(id)</t>
         </is>
       </c>
-      <c r="F201" s="23" t="inlineStr">
+      <c r="F201" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6476,19 +6435,19 @@
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr"/>
-      <c r="B202" s="17" t="inlineStr">
+      <c r="B202" s="16" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C202" s="21" t="inlineStr">
+      <c r="C202" s="20" t="inlineStr">
         <is>
           <t>varchar(160)</t>
         </is>
       </c>
-      <c r="D202" s="22" t="inlineStr"/>
-      <c r="E202" s="19" t="inlineStr"/>
-      <c r="F202" s="20" t="inlineStr">
+      <c r="D202" s="21" t="inlineStr"/>
+      <c r="E202" s="18" t="inlineStr"/>
+      <c r="F202" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6497,19 +6456,19 @@
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr"/>
-      <c r="B203" s="17" t="inlineStr">
+      <c r="B203" s="16" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C203" s="17" t="inlineStr">
+      <c r="C203" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D203" s="22" t="inlineStr"/>
-      <c r="E203" s="19" t="inlineStr"/>
-      <c r="F203" s="23" t="inlineStr">
+      <c r="D203" s="21" t="inlineStr"/>
+      <c r="E203" s="18" t="inlineStr"/>
+      <c r="F203" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6518,19 +6477,19 @@
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr"/>
-      <c r="B204" s="17" t="inlineStr">
+      <c r="B204" s="16" t="inlineStr">
         <is>
           <t>due_date</t>
         </is>
       </c>
-      <c r="C204" s="17" t="inlineStr">
+      <c r="C204" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D204" s="22" t="inlineStr"/>
-      <c r="E204" s="19" t="inlineStr"/>
-      <c r="F204" s="23" t="inlineStr">
+      <c r="D204" s="21" t="inlineStr"/>
+      <c r="E204" s="18" t="inlineStr"/>
+      <c r="F204" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6539,27 +6498,27 @@
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr"/>
-      <c r="B205" s="17" t="inlineStr">
+      <c r="B205" s="16" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="C205" s="17" t="inlineStr">
+      <c r="C205" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D205" s="24" t="inlineStr">
+      <c r="D205" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E205" s="19" t="inlineStr">
+      <c r="E205" s="18" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
       </c>
-      <c r="F205" s="20" t="inlineStr">
+      <c r="F205" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6568,19 +6527,19 @@
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr"/>
-      <c r="B206" s="17" t="inlineStr">
+      <c r="B206" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C206" s="21" t="inlineStr">
+      <c r="C206" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D206" s="22" t="inlineStr"/>
-      <c r="E206" s="19" t="inlineStr"/>
-      <c r="F206" s="20" t="inlineStr">
+      <c r="D206" s="21" t="inlineStr"/>
+      <c r="E206" s="18" t="inlineStr"/>
+      <c r="F206" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6588,37 +6547,37 @@
       <c r="G206" s="4" t="inlineStr"/>
     </row>
     <row r="207" ht="4" customHeight="1">
-      <c r="A207" s="25" t="n"/>
-      <c r="B207" s="25" t="n"/>
-      <c r="C207" s="25" t="n"/>
-      <c r="D207" s="25" t="n"/>
-      <c r="E207" s="25" t="n"/>
-      <c r="F207" s="25" t="n"/>
-      <c r="G207" s="25" t="n"/>
+      <c r="A207" s="24" t="n"/>
+      <c r="B207" s="24" t="n"/>
+      <c r="C207" s="24" t="n"/>
+      <c r="D207" s="24" t="n"/>
+      <c r="E207" s="24" t="n"/>
+      <c r="F207" s="24" t="n"/>
+      <c r="G207" s="24" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="15" t="inlineStr">
+      <c r="A208" s="14" t="inlineStr">
         <is>
           <t>homework_submission</t>
         </is>
       </c>
-      <c r="B208" s="16" t="inlineStr">
+      <c r="B208" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C208" s="17" t="inlineStr">
+      <c r="C208" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D208" s="18" t="inlineStr">
+      <c r="D208" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E208" s="19" t="inlineStr"/>
-      <c r="F208" s="20" t="inlineStr">
+      <c r="E208" s="18" t="inlineStr"/>
+      <c r="F208" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6627,27 +6586,27 @@
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr"/>
-      <c r="B209" s="17" t="inlineStr">
+      <c r="B209" s="16" t="inlineStr">
         <is>
           <t>homework_id</t>
         </is>
       </c>
-      <c r="C209" s="17" t="inlineStr">
+      <c r="C209" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D209" s="24" t="inlineStr">
+      <c r="D209" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E209" s="19" t="inlineStr">
+      <c r="E209" s="18" t="inlineStr">
         <is>
           <t>homework(id)</t>
         </is>
       </c>
-      <c r="F209" s="20" t="inlineStr">
+      <c r="F209" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6656,27 +6615,27 @@
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr"/>
-      <c r="B210" s="17" t="inlineStr">
+      <c r="B210" s="16" t="inlineStr">
         <is>
           <t>student_id</t>
         </is>
       </c>
-      <c r="C210" s="17" t="inlineStr">
+      <c r="C210" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D210" s="24" t="inlineStr">
+      <c r="D210" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E210" s="19" t="inlineStr">
+      <c r="E210" s="18" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
       </c>
-      <c r="F210" s="20" t="inlineStr">
+      <c r="F210" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6685,19 +6644,19 @@
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr"/>
-      <c r="B211" s="17" t="inlineStr">
+      <c r="B211" s="16" t="inlineStr">
         <is>
           <t>file_url</t>
         </is>
       </c>
-      <c r="C211" s="21" t="inlineStr">
+      <c r="C211" s="20" t="inlineStr">
         <is>
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="D211" s="22" t="inlineStr"/>
-      <c r="E211" s="19" t="inlineStr"/>
-      <c r="F211" s="23" t="inlineStr">
+      <c r="D211" s="21" t="inlineStr"/>
+      <c r="E211" s="18" t="inlineStr"/>
+      <c r="F211" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6706,19 +6665,19 @@
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr"/>
-      <c r="B212" s="17" t="inlineStr">
+      <c r="B212" s="16" t="inlineStr">
         <is>
           <t>external_link</t>
         </is>
       </c>
-      <c r="C212" s="21" t="inlineStr">
+      <c r="C212" s="20" t="inlineStr">
         <is>
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="D212" s="22" t="inlineStr"/>
-      <c r="E212" s="19" t="inlineStr"/>
-      <c r="F212" s="23" t="inlineStr">
+      <c r="D212" s="21" t="inlineStr"/>
+      <c r="E212" s="18" t="inlineStr"/>
+      <c r="F212" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6727,19 +6686,19 @@
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr"/>
-      <c r="B213" s="17" t="inlineStr">
+      <c r="B213" s="16" t="inlineStr">
         <is>
           <t>submitted_at</t>
         </is>
       </c>
-      <c r="C213" s="21" t="inlineStr">
+      <c r="C213" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D213" s="22" t="inlineStr"/>
-      <c r="E213" s="19" t="inlineStr"/>
-      <c r="F213" s="23" t="inlineStr">
+      <c r="D213" s="21" t="inlineStr"/>
+      <c r="E213" s="18" t="inlineStr"/>
+      <c r="F213" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6748,19 +6707,19 @@
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr"/>
-      <c r="B214" s="17" t="inlineStr">
+      <c r="B214" s="16" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C214" s="21" t="inlineStr">
+      <c r="C214" s="20" t="inlineStr">
         <is>
           <t>homework_status</t>
         </is>
       </c>
-      <c r="D214" s="22" t="inlineStr"/>
-      <c r="E214" s="19" t="inlineStr"/>
-      <c r="F214" s="20" t="inlineStr">
+      <c r="D214" s="21" t="inlineStr"/>
+      <c r="E214" s="18" t="inlineStr"/>
+      <c r="F214" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6773,19 +6732,19 @@
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr"/>
-      <c r="B215" s="17" t="inlineStr">
+      <c r="B215" s="16" t="inlineStr">
         <is>
           <t>grade</t>
         </is>
       </c>
-      <c r="C215" s="21" t="inlineStr">
+      <c r="C215" s="20" t="inlineStr">
         <is>
           <t>numeric(5,2)</t>
         </is>
       </c>
-      <c r="D215" s="22" t="inlineStr"/>
-      <c r="E215" s="19" t="inlineStr"/>
-      <c r="F215" s="23" t="inlineStr">
+      <c r="D215" s="21" t="inlineStr"/>
+      <c r="E215" s="18" t="inlineStr"/>
+      <c r="F215" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6794,19 +6753,19 @@
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr"/>
-      <c r="B216" s="17" t="inlineStr">
+      <c r="B216" s="16" t="inlineStr">
         <is>
           <t>feedback</t>
         </is>
       </c>
-      <c r="C216" s="17" t="inlineStr">
+      <c r="C216" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D216" s="22" t="inlineStr"/>
-      <c r="E216" s="19" t="inlineStr"/>
-      <c r="F216" s="23" t="inlineStr">
+      <c r="D216" s="21" t="inlineStr"/>
+      <c r="E216" s="18" t="inlineStr"/>
+      <c r="F216" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6815,27 +6774,27 @@
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr"/>
-      <c r="B217" s="17" t="inlineStr">
+      <c r="B217" s="16" t="inlineStr">
         <is>
           <t>reviewed_by</t>
         </is>
       </c>
-      <c r="C217" s="17" t="inlineStr">
+      <c r="C217" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D217" s="24" t="inlineStr">
+      <c r="D217" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E217" s="19" t="inlineStr">
+      <c r="E217" s="18" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
       </c>
-      <c r="F217" s="23" t="inlineStr">
+      <c r="F217" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6844,23 +6803,23 @@
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr"/>
-      <c r="B218" s="17" t="inlineStr">
+      <c r="B218" s="16" t="inlineStr">
         <is>
           <t>uq_sub</t>
         </is>
       </c>
-      <c r="C218" s="17" t="inlineStr">
+      <c r="C218" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D218" s="26" t="inlineStr">
+      <c r="D218" s="25" t="inlineStr">
         <is>
           <t>UQ</t>
         </is>
       </c>
-      <c r="E218" s="19" t="inlineStr"/>
-      <c r="F218" s="23" t="inlineStr"/>
+      <c r="E218" s="18" t="inlineStr"/>
+      <c r="F218" s="22" t="inlineStr"/>
       <c r="G218" s="4" t="inlineStr">
         <is>
           <t>UNIQUE(homework_id, student_id)</t>
@@ -6868,37 +6827,37 @@
       </c>
     </row>
     <row r="219" ht="4" customHeight="1">
-      <c r="A219" s="25" t="n"/>
-      <c r="B219" s="25" t="n"/>
-      <c r="C219" s="25" t="n"/>
-      <c r="D219" s="25" t="n"/>
-      <c r="E219" s="25" t="n"/>
-      <c r="F219" s="25" t="n"/>
-      <c r="G219" s="25" t="n"/>
+      <c r="A219" s="24" t="n"/>
+      <c r="B219" s="24" t="n"/>
+      <c r="C219" s="24" t="n"/>
+      <c r="D219" s="24" t="n"/>
+      <c r="E219" s="24" t="n"/>
+      <c r="F219" s="24" t="n"/>
+      <c r="G219" s="24" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="15" t="inlineStr">
+      <c r="A220" s="14" t="inlineStr">
         <is>
           <t>stevecoin_transaction</t>
         </is>
       </c>
-      <c r="B220" s="16" t="inlineStr">
+      <c r="B220" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C220" s="17" t="inlineStr">
+      <c r="C220" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D220" s="18" t="inlineStr">
+      <c r="D220" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E220" s="19" t="inlineStr"/>
-      <c r="F220" s="20" t="inlineStr">
+      <c r="E220" s="18" t="inlineStr"/>
+      <c r="F220" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6907,27 +6866,27 @@
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr"/>
-      <c r="B221" s="17" t="inlineStr">
+      <c r="B221" s="16" t="inlineStr">
         <is>
           <t>student_id</t>
         </is>
       </c>
-      <c r="C221" s="17" t="inlineStr">
+      <c r="C221" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D221" s="24" t="inlineStr">
+      <c r="D221" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E221" s="19" t="inlineStr">
+      <c r="E221" s="18" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
       </c>
-      <c r="F221" s="20" t="inlineStr">
+      <c r="F221" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6936,19 +6895,19 @@
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr"/>
-      <c r="B222" s="17" t="inlineStr">
+      <c r="B222" s="16" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C222" s="17" t="inlineStr">
+      <c r="C222" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D222" s="22" t="inlineStr"/>
-      <c r="E222" s="19" t="inlineStr"/>
-      <c r="F222" s="20" t="inlineStr">
+      <c r="D222" s="21" t="inlineStr"/>
+      <c r="E222" s="18" t="inlineStr"/>
+      <c r="F222" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -6961,19 +6920,19 @@
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr"/>
-      <c r="B223" s="17" t="inlineStr">
+      <c r="B223" s="16" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="C223" s="21" t="inlineStr">
+      <c r="C223" s="20" t="inlineStr">
         <is>
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="D223" s="22" t="inlineStr"/>
-      <c r="E223" s="19" t="inlineStr"/>
-      <c r="F223" s="23" t="inlineStr">
+      <c r="D223" s="21" t="inlineStr"/>
+      <c r="E223" s="18" t="inlineStr"/>
+      <c r="F223" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -6982,27 +6941,27 @@
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr"/>
-      <c r="B224" s="17" t="inlineStr">
+      <c r="B224" s="16" t="inlineStr">
         <is>
           <t>lesson_id</t>
         </is>
       </c>
-      <c r="C224" s="17" t="inlineStr">
+      <c r="C224" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D224" s="24" t="inlineStr">
+      <c r="D224" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E224" s="19" t="inlineStr">
+      <c r="E224" s="18" t="inlineStr">
         <is>
           <t>lesson(id)</t>
         </is>
       </c>
-      <c r="F224" s="23" t="inlineStr">
+      <c r="F224" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7011,27 +6970,27 @@
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr"/>
-      <c r="B225" s="17" t="inlineStr">
+      <c r="B225" s="16" t="inlineStr">
         <is>
           <t>awarded_by</t>
         </is>
       </c>
-      <c r="C225" s="17" t="inlineStr">
+      <c r="C225" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D225" s="24" t="inlineStr">
+      <c r="D225" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E225" s="19" t="inlineStr">
+      <c r="E225" s="18" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
       </c>
-      <c r="F225" s="23" t="inlineStr">
+      <c r="F225" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7040,19 +6999,19 @@
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr"/>
-      <c r="B226" s="17" t="inlineStr">
+      <c r="B226" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C226" s="21" t="inlineStr">
+      <c r="C226" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D226" s="22" t="inlineStr"/>
-      <c r="E226" s="19" t="inlineStr"/>
-      <c r="F226" s="20" t="inlineStr">
+      <c r="D226" s="21" t="inlineStr"/>
+      <c r="E226" s="18" t="inlineStr"/>
+      <c r="F226" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -7060,37 +7019,37 @@
       <c r="G226" s="4" t="inlineStr"/>
     </row>
     <row r="227" ht="4" customHeight="1">
-      <c r="A227" s="25" t="n"/>
-      <c r="B227" s="25" t="n"/>
-      <c r="C227" s="25" t="n"/>
-      <c r="D227" s="25" t="n"/>
-      <c r="E227" s="25" t="n"/>
-      <c r="F227" s="25" t="n"/>
-      <c r="G227" s="25" t="n"/>
+      <c r="A227" s="24" t="n"/>
+      <c r="B227" s="24" t="n"/>
+      <c r="C227" s="24" t="n"/>
+      <c r="D227" s="24" t="n"/>
+      <c r="E227" s="24" t="n"/>
+      <c r="F227" s="24" t="n"/>
+      <c r="G227" s="24" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="15" t="inlineStr">
+      <c r="A228" s="14" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="B228" s="16" t="inlineStr">
+      <c r="B228" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C228" s="17" t="inlineStr">
+      <c r="C228" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D228" s="18" t="inlineStr">
+      <c r="D228" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E228" s="19" t="inlineStr"/>
-      <c r="F228" s="20" t="inlineStr">
+      <c r="E228" s="18" t="inlineStr"/>
+      <c r="F228" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -7099,19 +7058,19 @@
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr"/>
-      <c r="B229" s="17" t="inlineStr">
+      <c r="B229" s="16" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C229" s="21" t="inlineStr">
+      <c r="C229" s="20" t="inlineStr">
         <is>
           <t>varchar(160)</t>
         </is>
       </c>
-      <c r="D229" s="22" t="inlineStr"/>
-      <c r="E229" s="19" t="inlineStr"/>
-      <c r="F229" s="20" t="inlineStr">
+      <c r="D229" s="21" t="inlineStr"/>
+      <c r="E229" s="18" t="inlineStr"/>
+      <c r="F229" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -7120,19 +7079,19 @@
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr"/>
-      <c r="B230" s="17" t="inlineStr">
+      <c r="B230" s="16" t="inlineStr">
         <is>
           <t>track</t>
         </is>
       </c>
-      <c r="C230" s="21" t="inlineStr">
+      <c r="C230" s="20" t="inlineStr">
         <is>
           <t>varchar(80)</t>
         </is>
       </c>
-      <c r="D230" s="22" t="inlineStr"/>
-      <c r="E230" s="19" t="inlineStr"/>
-      <c r="F230" s="23" t="inlineStr">
+      <c r="D230" s="21" t="inlineStr"/>
+      <c r="E230" s="18" t="inlineStr"/>
+      <c r="F230" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7145,27 +7104,27 @@
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr"/>
-      <c r="B231" s="17" t="inlineStr">
+      <c r="B231" s="16" t="inlineStr">
         <is>
           <t>branch_id</t>
         </is>
       </c>
-      <c r="C231" s="17" t="inlineStr">
+      <c r="C231" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D231" s="24" t="inlineStr">
+      <c r="D231" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E231" s="19" t="inlineStr">
+      <c r="E231" s="18" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
       </c>
-      <c r="F231" s="23" t="inlineStr">
+      <c r="F231" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7178,19 +7137,19 @@
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr"/>
-      <c r="B232" s="17" t="inlineStr">
+      <c r="B232" s="16" t="inlineStr">
         <is>
           <t>starts_on</t>
         </is>
       </c>
-      <c r="C232" s="17" t="inlineStr">
+      <c r="C232" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D232" s="22" t="inlineStr"/>
-      <c r="E232" s="19" t="inlineStr"/>
-      <c r="F232" s="23" t="inlineStr">
+      <c r="D232" s="21" t="inlineStr"/>
+      <c r="E232" s="18" t="inlineStr"/>
+      <c r="F232" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7199,19 +7158,19 @@
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr"/>
-      <c r="B233" s="17" t="inlineStr">
+      <c r="B233" s="16" t="inlineStr">
         <is>
           <t>ends_on</t>
         </is>
       </c>
-      <c r="C233" s="17" t="inlineStr">
+      <c r="C233" s="16" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D233" s="22" t="inlineStr"/>
-      <c r="E233" s="19" t="inlineStr"/>
-      <c r="F233" s="23" t="inlineStr">
+      <c r="D233" s="21" t="inlineStr"/>
+      <c r="E233" s="18" t="inlineStr"/>
+      <c r="F233" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7220,19 +7179,19 @@
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr"/>
-      <c r="B234" s="17" t="inlineStr">
+      <c r="B234" s="16" t="inlineStr">
         <is>
           <t>coins_participation</t>
         </is>
       </c>
-      <c r="C234" s="17" t="inlineStr">
+      <c r="C234" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D234" s="22" t="inlineStr"/>
-      <c r="E234" s="19" t="inlineStr"/>
-      <c r="F234" s="23" t="inlineStr">
+      <c r="D234" s="21" t="inlineStr"/>
+      <c r="E234" s="18" t="inlineStr"/>
+      <c r="F234" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7241,19 +7200,19 @@
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr"/>
-      <c r="B235" s="17" t="inlineStr">
+      <c r="B235" s="16" t="inlineStr">
         <is>
           <t>coins_win</t>
         </is>
       </c>
-      <c r="C235" s="17" t="inlineStr">
+      <c r="C235" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D235" s="22" t="inlineStr"/>
-      <c r="E235" s="19" t="inlineStr"/>
-      <c r="F235" s="23" t="inlineStr">
+      <c r="D235" s="21" t="inlineStr"/>
+      <c r="E235" s="18" t="inlineStr"/>
+      <c r="F235" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7262,19 +7221,19 @@
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr"/>
-      <c r="B236" s="17" t="inlineStr">
+      <c r="B236" s="16" t="inlineStr">
         <is>
           <t>coins_completion</t>
         </is>
       </c>
-      <c r="C236" s="17" t="inlineStr">
+      <c r="C236" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D236" s="22" t="inlineStr"/>
-      <c r="E236" s="19" t="inlineStr"/>
-      <c r="F236" s="23" t="inlineStr">
+      <c r="D236" s="21" t="inlineStr"/>
+      <c r="E236" s="18" t="inlineStr"/>
+      <c r="F236" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7283,19 +7242,19 @@
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr"/>
-      <c r="B237" s="17" t="inlineStr">
+      <c r="B237" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C237" s="21" t="inlineStr">
+      <c r="C237" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D237" s="22" t="inlineStr"/>
-      <c r="E237" s="19" t="inlineStr"/>
-      <c r="F237" s="20" t="inlineStr">
+      <c r="D237" s="21" t="inlineStr"/>
+      <c r="E237" s="18" t="inlineStr"/>
+      <c r="F237" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -7303,37 +7262,37 @@
       <c r="G237" s="4" t="inlineStr"/>
     </row>
     <row r="238" ht="4" customHeight="1">
-      <c r="A238" s="25" t="n"/>
-      <c r="B238" s="25" t="n"/>
-      <c r="C238" s="25" t="n"/>
-      <c r="D238" s="25" t="n"/>
-      <c r="E238" s="25" t="n"/>
-      <c r="F238" s="25" t="n"/>
-      <c r="G238" s="25" t="n"/>
+      <c r="A238" s="24" t="n"/>
+      <c r="B238" s="24" t="n"/>
+      <c r="C238" s="24" t="n"/>
+      <c r="D238" s="24" t="n"/>
+      <c r="E238" s="24" t="n"/>
+      <c r="F238" s="24" t="n"/>
+      <c r="G238" s="24" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="15" t="inlineStr">
+      <c r="A239" s="14" t="inlineStr">
         <is>
           <t>project_participation</t>
         </is>
       </c>
-      <c r="B239" s="16" t="inlineStr">
+      <c r="B239" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C239" s="17" t="inlineStr">
+      <c r="C239" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D239" s="18" t="inlineStr">
+      <c r="D239" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E239" s="19" t="inlineStr"/>
-      <c r="F239" s="20" t="inlineStr">
+      <c r="E239" s="18" t="inlineStr"/>
+      <c r="F239" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -7342,27 +7301,27 @@
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr"/>
-      <c r="B240" s="17" t="inlineStr">
+      <c r="B240" s="16" t="inlineStr">
         <is>
           <t>project_id</t>
         </is>
       </c>
-      <c r="C240" s="17" t="inlineStr">
+      <c r="C240" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D240" s="24" t="inlineStr">
+      <c r="D240" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E240" s="19" t="inlineStr">
+      <c r="E240" s="18" t="inlineStr">
         <is>
           <t>project(id)</t>
         </is>
       </c>
-      <c r="F240" s="20" t="inlineStr">
+      <c r="F240" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -7371,27 +7330,27 @@
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr"/>
-      <c r="B241" s="17" t="inlineStr">
+      <c r="B241" s="16" t="inlineStr">
         <is>
           <t>student_id</t>
         </is>
       </c>
-      <c r="C241" s="17" t="inlineStr">
+      <c r="C241" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D241" s="24" t="inlineStr">
+      <c r="D241" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E241" s="19" t="inlineStr">
+      <c r="E241" s="18" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
       </c>
-      <c r="F241" s="20" t="inlineStr">
+      <c r="F241" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -7400,19 +7359,19 @@
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr"/>
-      <c r="B242" s="17" t="inlineStr">
+      <c r="B242" s="16" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="C242" s="21" t="inlineStr">
+      <c r="C242" s="20" t="inlineStr">
         <is>
           <t>project_result</t>
         </is>
       </c>
-      <c r="D242" s="22" t="inlineStr"/>
-      <c r="E242" s="19" t="inlineStr"/>
-      <c r="F242" s="23" t="inlineStr">
+      <c r="D242" s="21" t="inlineStr"/>
+      <c r="E242" s="18" t="inlineStr"/>
+      <c r="F242" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7425,19 +7384,19 @@
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr"/>
-      <c r="B243" s="17" t="inlineStr">
+      <c r="B243" s="16" t="inlineStr">
         <is>
           <t>coins_awarded</t>
         </is>
       </c>
-      <c r="C243" s="17" t="inlineStr">
+      <c r="C243" s="16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D243" s="22" t="inlineStr"/>
-      <c r="E243" s="19" t="inlineStr"/>
-      <c r="F243" s="23" t="inlineStr">
+      <c r="D243" s="21" t="inlineStr"/>
+      <c r="E243" s="18" t="inlineStr"/>
+      <c r="F243" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7446,23 +7405,23 @@
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr"/>
-      <c r="B244" s="17" t="inlineStr">
+      <c r="B244" s="16" t="inlineStr">
         <is>
           <t>uq_pp</t>
         </is>
       </c>
-      <c r="C244" s="17" t="inlineStr">
+      <c r="C244" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D244" s="26" t="inlineStr">
+      <c r="D244" s="25" t="inlineStr">
         <is>
           <t>UQ</t>
         </is>
       </c>
-      <c r="E244" s="19" t="inlineStr"/>
-      <c r="F244" s="23" t="inlineStr"/>
+      <c r="E244" s="18" t="inlineStr"/>
+      <c r="F244" s="22" t="inlineStr"/>
       <c r="G244" s="4" t="inlineStr">
         <is>
           <t>UNIQUE(project_id, student_id)</t>
@@ -7470,37 +7429,37 @@
       </c>
     </row>
     <row r="245" ht="4" customHeight="1">
-      <c r="A245" s="25" t="n"/>
-      <c r="B245" s="25" t="n"/>
-      <c r="C245" s="25" t="n"/>
-      <c r="D245" s="25" t="n"/>
-      <c r="E245" s="25" t="n"/>
-      <c r="F245" s="25" t="n"/>
-      <c r="G245" s="25" t="n"/>
+      <c r="A245" s="24" t="n"/>
+      <c r="B245" s="24" t="n"/>
+      <c r="C245" s="24" t="n"/>
+      <c r="D245" s="24" t="n"/>
+      <c r="E245" s="24" t="n"/>
+      <c r="F245" s="24" t="n"/>
+      <c r="G245" s="24" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="15" t="inlineStr">
+      <c r="A246" s="14" t="inlineStr">
         <is>
           <t>subscription</t>
         </is>
       </c>
-      <c r="B246" s="16" t="inlineStr">
+      <c r="B246" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C246" s="17" t="inlineStr">
+      <c r="C246" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D246" s="18" t="inlineStr">
+      <c r="D246" s="17" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="E246" s="19" t="inlineStr"/>
-      <c r="F246" s="20" t="inlineStr">
+      <c r="E246" s="18" t="inlineStr"/>
+      <c r="F246" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -7509,27 +7468,27 @@
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr"/>
-      <c r="B247" s="17" t="inlineStr">
+      <c r="B247" s="16" t="inlineStr">
         <is>
           <t>student_id</t>
         </is>
       </c>
-      <c r="C247" s="17" t="inlineStr">
+      <c r="C247" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D247" s="24" t="inlineStr">
+      <c r="D247" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E247" s="19" t="inlineStr">
+      <c r="E247" s="18" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
       </c>
-      <c r="F247" s="20" t="inlineStr">
+      <c r="F247" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -7538,27 +7497,27 @@
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr"/>
-      <c r="B248" s="17" t="inlineStr">
+      <c r="B248" s="16" t="inlineStr">
         <is>
           <t>parent_id</t>
         </is>
       </c>
-      <c r="C248" s="17" t="inlineStr">
+      <c r="C248" s="16" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="D248" s="24" t="inlineStr">
+      <c r="D248" s="23" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="E248" s="19" t="inlineStr">
+      <c r="E248" s="18" t="inlineStr">
         <is>
           <t>parent(id)</t>
         </is>
       </c>
-      <c r="F248" s="23" t="inlineStr">
+      <c r="F248" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7567,19 +7526,19 @@
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr"/>
-      <c r="B249" s="17" t="inlineStr">
+      <c r="B249" s="16" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
       </c>
-      <c r="C249" s="17" t="inlineStr">
+      <c r="C249" s="16" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="D249" s="22" t="inlineStr"/>
-      <c r="E249" s="19" t="inlineStr"/>
-      <c r="F249" s="20" t="inlineStr">
+      <c r="D249" s="21" t="inlineStr"/>
+      <c r="E249" s="18" t="inlineStr"/>
+      <c r="F249" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -7588,19 +7547,19 @@
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr"/>
-      <c r="B250" s="17" t="inlineStr">
+      <c r="B250" s="16" t="inlineStr">
         <is>
           <t>activated_at</t>
         </is>
       </c>
-      <c r="C250" s="21" t="inlineStr">
+      <c r="C250" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D250" s="22" t="inlineStr"/>
-      <c r="E250" s="19" t="inlineStr"/>
-      <c r="F250" s="23" t="inlineStr">
+      <c r="D250" s="21" t="inlineStr"/>
+      <c r="E250" s="18" t="inlineStr"/>
+      <c r="F250" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7609,19 +7568,19 @@
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr"/>
-      <c r="B251" s="17" t="inlineStr">
+      <c r="B251" s="16" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C251" s="21" t="inlineStr">
+      <c r="C251" s="20" t="inlineStr">
         <is>
           <t>numeric(10,2)</t>
         </is>
       </c>
-      <c r="D251" s="22" t="inlineStr"/>
-      <c r="E251" s="19" t="inlineStr"/>
-      <c r="F251" s="23" t="inlineStr">
+      <c r="D251" s="21" t="inlineStr"/>
+      <c r="E251" s="18" t="inlineStr"/>
+      <c r="F251" s="22" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
@@ -7630,19 +7589,19 @@
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr"/>
-      <c r="B252" s="17" t="inlineStr">
+      <c r="B252" s="16" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C252" s="21" t="inlineStr">
+      <c r="C252" s="20" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="D252" s="22" t="inlineStr"/>
-      <c r="E252" s="19" t="inlineStr"/>
-      <c r="F252" s="20" t="inlineStr">
+      <c r="D252" s="21" t="inlineStr"/>
+      <c r="E252" s="18" t="inlineStr"/>
+      <c r="F252" s="19" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
@@ -7650,170 +7609,16 @@
       <c r="G252" s="4" t="inlineStr"/>
     </row>
     <row r="253" ht="4" customHeight="1">
-      <c r="A253" s="25" t="n"/>
-      <c r="B253" s="25" t="n"/>
-      <c r="C253" s="25" t="n"/>
-      <c r="D253" s="25" t="n"/>
-      <c r="E253" s="25" t="n"/>
-      <c r="F253" s="25" t="n"/>
-      <c r="G253" s="25" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="15" t="inlineStr">
-        <is>
-          <t>module_progress</t>
-        </is>
-      </c>
-      <c r="B254" s="17" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="C254" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D254" s="24" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E254" s="19" t="inlineStr">
-        <is>
-          <t>student(id)</t>
-        </is>
-      </c>
-      <c r="F254" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G254" s="4" t="inlineStr">
-        <is>
-          <t>Part of composite key</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="3" t="inlineStr"/>
-      <c r="B255" s="17" t="inlineStr">
-        <is>
-          <t>module_id</t>
-        </is>
-      </c>
-      <c r="C255" s="17" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="D255" s="24" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E255" s="19" t="inlineStr">
-        <is>
-          <t>module(id)</t>
-        </is>
-      </c>
-      <c r="F255" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G255" s="4" t="inlineStr">
-        <is>
-          <t>Part of composite key</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="3" t="inlineStr"/>
-      <c r="B256" s="17" t="inlineStr">
-        <is>
-          <t>completed_lectures</t>
-        </is>
-      </c>
-      <c r="C256" s="17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D256" s="22" t="inlineStr"/>
-      <c r="E256" s="19" t="inlineStr"/>
-      <c r="F256" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G256" s="4" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="3" t="inlineStr"/>
-      <c r="B257" s="17" t="inlineStr">
-        <is>
-          <t>total_lectures</t>
-        </is>
-      </c>
-      <c r="C257" s="17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D257" s="22" t="inlineStr"/>
-      <c r="E257" s="19" t="inlineStr"/>
-      <c r="F257" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G257" s="4" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="3" t="inlineStr"/>
-      <c r="B258" s="17" t="inlineStr">
-        <is>
-          <t>progress_pct</t>
-        </is>
-      </c>
-      <c r="C258" s="21" t="inlineStr">
-        <is>
-          <t>numeric(5,2)</t>
-        </is>
-      </c>
-      <c r="D258" s="22" t="inlineStr"/>
-      <c r="E258" s="19" t="inlineStr"/>
-      <c r="F258" s="20" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="G258" s="4" t="inlineStr">
-        <is>
-          <t>Computed</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="4" customHeight="1">
-      <c r="A259" s="25" t="n"/>
-      <c r="B259" s="25" t="n"/>
-      <c r="C259" s="25" t="n"/>
-      <c r="D259" s="25" t="n"/>
-      <c r="E259" s="25" t="n"/>
-      <c r="F259" s="25" t="n"/>
-      <c r="G259" s="25" t="n"/>
+      <c r="A253" s="24" t="n"/>
+      <c r="B253" s="24" t="n"/>
+      <c r="C253" s="24" t="n"/>
+      <c r="D253" s="24" t="n"/>
+      <c r="E253" s="24" t="n"/>
+      <c r="F253" s="24" t="n"/>
+      <c r="G253" s="24" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G259"/>
+  <autoFilter ref="A1:G253"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7824,7 +7629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7887,7 +7692,7 @@
           <t>manager_id</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>staff_member(id)</t>
         </is>
@@ -7897,7 +7702,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -7922,7 +7727,7 @@
           <t>branch_id</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
@@ -7932,7 +7737,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -7957,7 +7762,7 @@
           <t>user_id</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>app_user(id)</t>
         </is>
@@ -7967,7 +7772,7 @@
           <t>1:1</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -7992,7 +7797,7 @@
           <t>branch_id</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
@@ -8002,7 +7807,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8027,7 +7832,7 @@
           <t>current_group_id</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>study_group(id)</t>
         </is>
@@ -8037,7 +7842,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8062,7 +7867,7 @@
           <t>intake_id</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>intake(id)</t>
         </is>
@@ -8072,7 +7877,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8097,7 +7902,7 @@
           <t>age_category_id</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>age_category(id)</t>
         </is>
@@ -8107,7 +7912,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8132,7 +7937,7 @@
           <t>alumni_category_id</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>age_category(id)</t>
         </is>
@@ -8142,7 +7947,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8167,7 +7972,7 @@
           <t>user_id</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>app_user(id)</t>
         </is>
@@ -8177,7 +7982,7 @@
           <t>1:1</t>
         </is>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8202,7 +8007,7 @@
           <t>student_id</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
@@ -8212,7 +8017,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8237,7 +8042,7 @@
           <t>parent_id</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>parent(id)</t>
         </is>
@@ -8247,7 +8052,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8272,7 +8077,7 @@
           <t>user_id</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>app_user(id)</t>
         </is>
@@ -8282,7 +8087,7 @@
           <t>1:1</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8307,7 +8112,7 @@
           <t>branch_id</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
@@ -8317,7 +8122,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8342,7 +8147,7 @@
           <t>user_id</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>app_user(id)</t>
         </is>
@@ -8352,7 +8157,7 @@
           <t>1:1</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8377,7 +8182,7 @@
           <t>branch_id</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
@@ -8387,7 +8192,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8412,7 +8217,7 @@
           <t>branch_id</t>
         </is>
       </c>
-      <c r="D17" s="29" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
@@ -8422,7 +8227,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8447,7 +8252,7 @@
           <t>age_category_id</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>age_category(id)</t>
         </is>
@@ -8457,7 +8262,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8482,7 +8287,7 @@
           <t>intake_id</t>
         </is>
       </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>intake(id)</t>
         </is>
@@ -8492,7 +8297,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F19" s="30" t="inlineStr">
+      <c r="F19" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8517,7 +8322,7 @@
           <t>module_id</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>module(id)</t>
         </is>
@@ -8527,7 +8332,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8552,7 +8357,7 @@
           <t>group_id</t>
         </is>
       </c>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>study_group(id)</t>
         </is>
@@ -8562,7 +8367,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F21" s="30" t="inlineStr">
+      <c r="F21" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8587,7 +8392,7 @@
           <t>student_id</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
@@ -8597,7 +8402,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8622,7 +8427,7 @@
           <t>age_category_id</t>
         </is>
       </c>
-      <c r="D23" s="29" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>age_category(id)</t>
         </is>
@@ -8632,7 +8437,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F23" s="30" t="inlineStr">
+      <c r="F23" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8657,7 +8462,7 @@
           <t>template_id</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>module_template(id)</t>
         </is>
@@ -8667,7 +8472,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8692,7 +8497,7 @@
           <t>intake_id</t>
         </is>
       </c>
-      <c r="D25" s="29" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>intake(id)</t>
         </is>
@@ -8702,7 +8507,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F25" s="30" t="inlineStr">
+      <c r="F25" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8727,7 +8532,7 @@
           <t>age_category_id</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="26" t="inlineStr">
         <is>
           <t>age_category(id)</t>
         </is>
@@ -8737,7 +8542,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F26" s="28" t="inlineStr">
+      <c r="F26" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8762,7 +8567,7 @@
           <t>template_id</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr">
         <is>
           <t>module_template(id)</t>
         </is>
@@ -8772,7 +8577,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr">
+      <c r="F27" s="29" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8797,7 +8602,7 @@
           <t>module_id</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>module(id)</t>
         </is>
@@ -8807,7 +8612,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F28" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8832,7 +8637,7 @@
           <t>template_lecture_id</t>
         </is>
       </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>template_lecture(id)</t>
         </is>
@@ -8842,7 +8647,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F29" s="30" t="inlineStr">
+      <c r="F29" s="29" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8867,7 +8672,7 @@
           <t>module_lecture_id</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D30" s="26" t="inlineStr">
         <is>
           <t>module_lecture(id)</t>
         </is>
@@ -8877,7 +8682,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="F30" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8902,7 +8707,7 @@
           <t>template_lecture_id</t>
         </is>
       </c>
-      <c r="D31" s="29" t="inlineStr">
+      <c r="D31" s="28" t="inlineStr">
         <is>
           <t>template_lecture(id)</t>
         </is>
@@ -8912,7 +8717,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="29" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -8937,7 +8742,7 @@
           <t>group_id</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D32" s="26" t="inlineStr">
         <is>
           <t>study_group(id)</t>
         </is>
@@ -8947,7 +8752,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -8972,7 +8777,7 @@
           <t>module_lecture_id</t>
         </is>
       </c>
-      <c r="D33" s="29" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>module_lecture(id)</t>
         </is>
@@ -8982,7 +8787,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F33" s="30" t="inlineStr">
+      <c r="F33" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9007,7 +8812,7 @@
           <t>trainer_id</t>
         </is>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="D34" s="26" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
@@ -9017,7 +8822,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="F34" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -9042,7 +8847,7 @@
           <t>lesson_id</t>
         </is>
       </c>
-      <c r="D35" s="29" t="inlineStr">
+      <c r="D35" s="28" t="inlineStr">
         <is>
           <t>lesson(id)</t>
         </is>
@@ -9052,7 +8857,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="F35" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9077,7 +8882,7 @@
           <t>student_id</t>
         </is>
       </c>
-      <c r="D36" s="27" t="inlineStr">
+      <c r="D36" s="26" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
@@ -9087,7 +8892,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F36" s="28" t="inlineStr">
+      <c r="F36" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9112,7 +8917,7 @@
           <t>recorded_by</t>
         </is>
       </c>
-      <c r="D37" s="29" t="inlineStr">
+      <c r="D37" s="28" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
@@ -9122,7 +8927,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F37" s="30" t="inlineStr">
+      <c r="F37" s="29" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -9147,7 +8952,7 @@
           <t>group_id</t>
         </is>
       </c>
-      <c r="D38" s="27" t="inlineStr">
+      <c r="D38" s="26" t="inlineStr">
         <is>
           <t>study_group(id)</t>
         </is>
@@ -9157,7 +8962,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F38" s="28" t="inlineStr">
+      <c r="F38" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9182,7 +8987,7 @@
           <t>module_lecture_id</t>
         </is>
       </c>
-      <c r="D39" s="29" t="inlineStr">
+      <c r="D39" s="28" t="inlineStr">
         <is>
           <t>module_lecture(id)</t>
         </is>
@@ -9192,7 +8997,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F39" s="30" t="inlineStr">
+      <c r="F39" s="29" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -9217,7 +9022,7 @@
           <t>exam_id</t>
         </is>
       </c>
-      <c r="D40" s="27" t="inlineStr">
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>exam(id)</t>
         </is>
@@ -9227,7 +9032,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F40" s="28" t="inlineStr">
+      <c r="F40" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9252,7 +9057,7 @@
           <t>student_id</t>
         </is>
       </c>
-      <c r="D41" s="29" t="inlineStr">
+      <c r="D41" s="28" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
@@ -9262,7 +9067,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F41" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9287,7 +9092,7 @@
           <t>recorded_by</t>
         </is>
       </c>
-      <c r="D42" s="27" t="inlineStr">
+      <c r="D42" s="26" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
@@ -9297,7 +9102,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F42" s="28" t="inlineStr">
+      <c r="F42" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -9322,7 +9127,7 @@
           <t>module_lecture_id</t>
         </is>
       </c>
-      <c r="D43" s="29" t="inlineStr">
+      <c r="D43" s="28" t="inlineStr">
         <is>
           <t>module_lecture(id)</t>
         </is>
@@ -9332,7 +9137,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F43" s="30" t="inlineStr">
+      <c r="F43" s="29" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -9357,7 +9162,7 @@
           <t>lesson_id</t>
         </is>
       </c>
-      <c r="D44" s="27" t="inlineStr">
+      <c r="D44" s="26" t="inlineStr">
         <is>
           <t>lesson(id)</t>
         </is>
@@ -9367,7 +9172,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F44" s="28" t="inlineStr">
+      <c r="F44" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -9392,7 +9197,7 @@
           <t>created_by</t>
         </is>
       </c>
-      <c r="D45" s="29" t="inlineStr">
+      <c r="D45" s="28" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
@@ -9402,7 +9207,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F45" s="30" t="inlineStr">
+      <c r="F45" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9427,7 +9232,7 @@
           <t>homework_id</t>
         </is>
       </c>
-      <c r="D46" s="27" t="inlineStr">
+      <c r="D46" s="26" t="inlineStr">
         <is>
           <t>homework(id)</t>
         </is>
@@ -9437,7 +9242,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F46" s="28" t="inlineStr">
+      <c r="F46" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9462,7 +9267,7 @@
           <t>student_id</t>
         </is>
       </c>
-      <c r="D47" s="29" t="inlineStr">
+      <c r="D47" s="28" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
@@ -9472,7 +9277,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F47" s="30" t="inlineStr">
+      <c r="F47" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9497,7 +9302,7 @@
           <t>reviewed_by</t>
         </is>
       </c>
-      <c r="D48" s="27" t="inlineStr">
+      <c r="D48" s="26" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
@@ -9507,7 +9312,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F48" s="28" t="inlineStr">
+      <c r="F48" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -9532,7 +9337,7 @@
           <t>student_id</t>
         </is>
       </c>
-      <c r="D49" s="29" t="inlineStr">
+      <c r="D49" s="28" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
@@ -9542,7 +9347,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F49" s="30" t="inlineStr">
+      <c r="F49" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9567,7 +9372,7 @@
           <t>lesson_id</t>
         </is>
       </c>
-      <c r="D50" s="27" t="inlineStr">
+      <c r="D50" s="26" t="inlineStr">
         <is>
           <t>lesson(id)</t>
         </is>
@@ -9577,7 +9382,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F50" s="28" t="inlineStr">
+      <c r="F50" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -9602,7 +9407,7 @@
           <t>awarded_by</t>
         </is>
       </c>
-      <c r="D51" s="29" t="inlineStr">
+      <c r="D51" s="28" t="inlineStr">
         <is>
           <t>trainer(id)</t>
         </is>
@@ -9612,7 +9417,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F51" s="30" t="inlineStr">
+      <c r="F51" s="29" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -9637,7 +9442,7 @@
           <t>branch_id</t>
         </is>
       </c>
-      <c r="D52" s="27" t="inlineStr">
+      <c r="D52" s="26" t="inlineStr">
         <is>
           <t>branch(id)</t>
         </is>
@@ -9647,7 +9452,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F52" s="28" t="inlineStr">
+      <c r="F52" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -9672,7 +9477,7 @@
           <t>project_id</t>
         </is>
       </c>
-      <c r="D53" s="29" t="inlineStr">
+      <c r="D53" s="28" t="inlineStr">
         <is>
           <t>project(id)</t>
         </is>
@@ -9682,7 +9487,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F53" s="30" t="inlineStr">
+      <c r="F53" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9707,7 +9512,7 @@
           <t>student_id</t>
         </is>
       </c>
-      <c r="D54" s="27" t="inlineStr">
+      <c r="D54" s="26" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
@@ -9717,7 +9522,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F54" s="28" t="inlineStr">
+      <c r="F54" s="27" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9742,7 +9547,7 @@
           <t>student_id</t>
         </is>
       </c>
-      <c r="D55" s="29" t="inlineStr">
+      <c r="D55" s="28" t="inlineStr">
         <is>
           <t>student(id)</t>
         </is>
@@ -9752,7 +9557,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F55" s="30" t="inlineStr">
+      <c r="F55" s="29" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
@@ -9777,7 +9582,7 @@
           <t>parent_id</t>
         </is>
       </c>
-      <c r="D56" s="27" t="inlineStr">
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>parent(id)</t>
         </is>
@@ -9787,7 +9592,7 @@
           <t>N:1</t>
         </is>
       </c>
-      <c r="F56" s="28" t="inlineStr">
+      <c r="F56" s="27" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
@@ -9799,150 +9604,80 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>module_progress</t>
-        </is>
-      </c>
-      <c r="C57" s="13" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="D57" s="29" t="inlineStr">
-        <is>
-          <t>student(id)</t>
-        </is>
-      </c>
-      <c r="E57" s="10" t="inlineStr">
-        <is>
-          <t>N:1</t>
-        </is>
-      </c>
-      <c r="F57" s="30" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t>Part of composite key</t>
+      <c r="B57" s="30" t="inlineStr">
+        <is>
+          <t>— Many-to-many resolutions —</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>module_progress</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>module_id</t>
-        </is>
-      </c>
-      <c r="D58" s="27" t="inlineStr">
-        <is>
-          <t>module(id)</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>N:1</t>
-        </is>
-      </c>
-      <c r="F58" s="28" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>Part of composite key</t>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>student_parent</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>student ↔ parent</t>
+        </is>
+      </c>
+      <c r="E58" s="21" t="inlineStr">
+        <is>
+          <t>M:N</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>via student_parent</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="31" t="inlineStr">
-        <is>
-          <t>— Many-to-many resolutions —</t>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>group_membership</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>student ↔ study_group</t>
+        </is>
+      </c>
+      <c r="E59" s="21" t="inlineStr">
+        <is>
+          <t>M:N</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>via group_membership</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>student_parent</t>
-        </is>
-      </c>
-      <c r="D60" s="19" t="inlineStr">
-        <is>
-          <t>student ↔ parent</t>
-        </is>
-      </c>
-      <c r="E60" s="22" t="inlineStr">
+          <t>project_participation</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>student ↔ project</t>
+        </is>
+      </c>
+      <c r="E60" s="21" t="inlineStr">
         <is>
           <t>M:N</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>via student_parent</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>group_membership</t>
-        </is>
-      </c>
-      <c r="D61" s="19" t="inlineStr">
-        <is>
-          <t>student ↔ study_group</t>
-        </is>
-      </c>
-      <c r="E61" s="22" t="inlineStr">
-        <is>
-          <t>M:N</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>via group_membership</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>project_participation</t>
-        </is>
-      </c>
-      <c r="D62" s="19" t="inlineStr">
-        <is>
-          <t>student ↔ project</t>
-        </is>
-      </c>
-      <c r="E62" s="22" t="inlineStr">
-        <is>
-          <t>M:N</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
           <t>via project_participation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G58"/>
+  <autoFilter ref="A1:G56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9953,7 +9688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10860,52 +10595,20 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>module_progress</t>
-        </is>
-      </c>
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C29" s="33" t="inlineStr">
-        <is>
-          <t>Student profile progress; dashboards</t>
-        </is>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="34" t="inlineStr">
-        <is>
-          <t>NONE — derived VIEW (no id; read-only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="31" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>Entities with NO CRUD point:</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>module_progress</t>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>— none: every remaining entity has at least one CRUD point —</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F29"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10942,7 +10645,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>user_role</t>
         </is>
@@ -10952,14 +10655,14 @@
           <t>student, parent, trainer, branch_manager, administrator</t>
         </is>
       </c>
-      <c r="C2" s="36" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>app_user.role, staff_member.role</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>student_status</t>
         </is>
@@ -10969,14 +10672,14 @@
           <t>active, waiting_list, suspended, graduated</t>
         </is>
       </c>
-      <c r="C3" s="38" t="inlineStr">
+      <c r="C3" s="34" t="inlineStr">
         <is>
           <t>student.status</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>group_status</t>
         </is>
@@ -10986,14 +10689,14 @@
           <t>current, starting, completed</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>study_group.status</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>lecture_type</t>
         </is>
@@ -11003,14 +10706,14 @@
           <t>training, midterm, final</t>
         </is>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>template_lecture, module_lecture</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>lesson_status</t>
         </is>
@@ -11020,14 +10723,14 @@
           <t>planned, in_progress, conducted</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>lesson.status</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>attendance_status</t>
         </is>
@@ -11037,14 +10740,14 @@
           <t>present, absent</t>
         </is>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>attendance.status</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>exam_type</t>
         </is>
@@ -11054,14 +10757,14 @@
           <t>quiz, midterm, final</t>
         </is>
       </c>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>exam.exam_type</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>homework_status</t>
         </is>
@@ -11071,14 +10774,14 @@
           <t>to_review, reviewed, overdue</t>
         </is>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>homework_submission.status</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>material_type</t>
         </is>
@@ -11088,14 +10791,14 @@
           <t>syllabus, lesson_plan, homework, exam, presentation, video, link</t>
         </is>
       </c>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>lecture_material.material_type</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>intake_season</t>
         </is>
@@ -11105,14 +10808,14 @@
           <t>spring, autumn</t>
         </is>
       </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>intake.season</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>relationship_type</t>
         </is>
@@ -11122,14 +10825,14 @@
           <t>mother, father, guardian, other</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>student_parent.relationship</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>project_result</t>
         </is>
@@ -11139,7 +10842,7 @@
           <t>participated, won, completed</t>
         </is>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>project_participation.result</t>
         </is>

--- a/SJA_ER_Model.xlsx
+++ b/SJA_ER_Model.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Menu access and CRUD rights are per user_group (group_menu_permission, group_resource_permission). A user belongs to one group; Students/Parents/Trainers are locked system groups tied to the dedicated interfaces.</t>
+          <t>Menu access and CRUD rights are per user_group (group_menu_permission, group_resource_permission). A user belongs to one group. Students/Parents/Trainers/Branch Manager are locked system groups, each with its own dedicated interface; every other (custom) group uses the Administrator interface restricted by its permissions.</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>ENUM: student/parent/trainer — set only for the 3 system groups; drives the dedicated interface</t>
+          <t>ENUM: student/parent/trainer/branch_manager — set only for the 4 locked system groups; drives the dedicated interface. NULL for custom groups (they use the Administrator interface)</t>
         </is>
       </c>
     </row>
@@ -11436,12 +11436,12 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>student, parent, trainer</t>
+          <t>student, parent, trainer, branch_manager</t>
         </is>
       </c>
       <c r="C2" s="32" t="inlineStr">
         <is>
-          <t>user_group.system_key (locked system groups)</t>
+          <t>user_group.system_key (locked system groups, each with its own interface)</t>
         </is>
       </c>
     </row>
